--- a/research/traditional_assets/database/data/jamaica/jamaica_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_beverage_soft.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1136592070985629</v>
+        <v>0.1134088090808165</v>
       </c>
       <c r="C2">
-        <v>556.5280929352853</v>
+        <v>553.011786652595</v>
       </c>
       <c r="D2">
-        <v>542.6280929352853</v>
+        <v>544.637786652595</v>
       </c>
       <c r="E2">
-        <v>-19.5</v>
+        <v>-13.974</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.526000000000001</v>
       </c>
       <c r="G2">
         <v>13.9</v>
@@ -1451,28 +1451,28 @@
         <v>36.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2779578</v>
       </c>
       <c r="N2">
-        <v>36.2</v>
+        <v>35.9220422</v>
       </c>
       <c r="O2">
-        <v>9.050000000000001</v>
+        <v>8.98051055</v>
       </c>
       <c r="P2">
-        <v>27.15</v>
+        <v>26.94153165</v>
       </c>
       <c r="Q2">
-        <v>34.34999999999999</v>
+        <v>34.14153165</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1136592070985629</v>
+        <v>0.1141732920008247</v>
       </c>
       <c r="T2">
-        <v>0.6562503962404382</v>
+        <v>0.6612219901513506</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>130.2355969143517</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1134088090808165</v>
+        <v>0.1131584110630701</v>
       </c>
       <c r="C3">
-        <v>553.011786652595</v>
+        <v>549.5104220324273</v>
       </c>
       <c r="D3">
-        <v>544.637786652595</v>
+        <v>546.6624220324273</v>
       </c>
       <c r="E3">
-        <v>-13.974</v>
+        <v>-8.448000000000002</v>
       </c>
       <c r="F3">
-        <v>5.526000000000001</v>
+        <v>11.052</v>
       </c>
       <c r="G3">
         <v>13.9</v>
@@ -1533,28 +1533,28 @@
         <v>36.2</v>
       </c>
       <c r="M3">
-        <v>0.2779578</v>
+        <v>0.5559156000000001</v>
       </c>
       <c r="N3">
-        <v>35.9220422</v>
+        <v>35.6440844</v>
       </c>
       <c r="O3">
-        <v>8.98051055</v>
+        <v>8.911021100000001</v>
       </c>
       <c r="P3">
-        <v>26.94153165</v>
+        <v>26.7330633</v>
       </c>
       <c r="Q3">
-        <v>34.14153165</v>
+        <v>33.9330633</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1141732920008247</v>
+        <v>0.1146978684317042</v>
       </c>
       <c r="T3">
-        <v>0.6612219901513506</v>
+        <v>0.6662950451624858</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>130.2355969143517</v>
+        <v>65.11779845717588</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1131584110630701</v>
+        <v>0.1129080130453237</v>
       </c>
       <c r="C4">
-        <v>549.5104220324273</v>
+        <v>546.024166328849</v>
       </c>
       <c r="D4">
-        <v>546.6624220324273</v>
+        <v>548.702166328849</v>
       </c>
       <c r="E4">
-        <v>-8.448000000000002</v>
+        <v>-2.922000000000004</v>
       </c>
       <c r="F4">
-        <v>11.052</v>
+        <v>16.578</v>
       </c>
       <c r="G4">
         <v>13.9</v>
@@ -1615,28 +1615,28 @@
         <v>36.2</v>
       </c>
       <c r="M4">
-        <v>0.5559156000000001</v>
+        <v>0.8338733999999999</v>
       </c>
       <c r="N4">
-        <v>35.6440844</v>
+        <v>35.3661266</v>
       </c>
       <c r="O4">
-        <v>8.911021100000001</v>
+        <v>8.84153165</v>
       </c>
       <c r="P4">
-        <v>26.7330633</v>
+        <v>26.52459495</v>
       </c>
       <c r="Q4">
-        <v>33.9330633</v>
+        <v>33.72459495</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1146978684317042</v>
+        <v>0.1152332608714677</v>
       </c>
       <c r="T4">
-        <v>0.6662950451624858</v>
+        <v>0.6714726992460154</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>65.11779845717588</v>
+        <v>43.41186563811726</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1129080130453237</v>
+        <v>0.1126576150275772</v>
       </c>
       <c r="C5">
-        <v>546.024166328849</v>
+        <v>542.5531893015535</v>
       </c>
       <c r="D5">
-        <v>548.702166328849</v>
+        <v>550.7571893015536</v>
       </c>
       <c r="E5">
-        <v>-2.922000000000004</v>
+        <v>2.603999999999999</v>
       </c>
       <c r="F5">
-        <v>16.578</v>
+        <v>22.104</v>
       </c>
       <c r="G5">
         <v>13.9</v>
@@ -1697,28 +1697,28 @@
         <v>36.2</v>
       </c>
       <c r="M5">
-        <v>0.8338733999999999</v>
+        <v>1.1118312</v>
       </c>
       <c r="N5">
-        <v>35.3661266</v>
+        <v>35.08816880000001</v>
       </c>
       <c r="O5">
-        <v>8.84153165</v>
+        <v>8.772042200000001</v>
       </c>
       <c r="P5">
-        <v>26.52459495</v>
+        <v>26.3161266</v>
       </c>
       <c r="Q5">
-        <v>33.72459495</v>
+        <v>33.5161266</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1152332608714677</v>
+        <v>0.115779807320393</v>
       </c>
       <c r="T5">
-        <v>0.6714726992460154</v>
+        <v>0.6767582211229519</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>43.41186563811726</v>
+        <v>32.55889922858793</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1126576150275772</v>
+        <v>0.1124072170098308</v>
       </c>
       <c r="C6">
-        <v>542.5531893015535</v>
+        <v>539.0976632629612</v>
       </c>
       <c r="D6">
-        <v>550.7571893015536</v>
+        <v>552.8276632629612</v>
       </c>
       <c r="E6">
-        <v>2.603999999999999</v>
+        <v>8.129999999999999</v>
       </c>
       <c r="F6">
-        <v>22.104</v>
+        <v>27.63</v>
       </c>
       <c r="G6">
         <v>13.9</v>
@@ -1779,28 +1779,28 @@
         <v>36.2</v>
       </c>
       <c r="M6">
-        <v>1.1118312</v>
+        <v>1.389789</v>
       </c>
       <c r="N6">
-        <v>35.08816880000001</v>
+        <v>34.810211</v>
       </c>
       <c r="O6">
-        <v>8.772042200000001</v>
+        <v>8.702552750000001</v>
       </c>
       <c r="P6">
-        <v>26.3161266</v>
+        <v>26.10765825</v>
       </c>
       <c r="Q6">
-        <v>33.5161266</v>
+        <v>33.30765825</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.115779807320393</v>
+        <v>0.1163378600103483</v>
       </c>
       <c r="T6">
-        <v>0.6767582211229519</v>
+        <v>0.6821550171446661</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.55889922858793</v>
+        <v>26.04711938287035</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1124072170098308</v>
+        <v>0.1121568189920845</v>
       </c>
       <c r="C7">
-        <v>539.0976632629612</v>
+        <v>535.6577631263817</v>
       </c>
       <c r="D7">
-        <v>552.8276632629612</v>
+        <v>554.9137631263818</v>
       </c>
       <c r="E7">
-        <v>8.129999999999999</v>
+        <v>13.656</v>
       </c>
       <c r="F7">
-        <v>27.63</v>
+        <v>33.15600000000001</v>
       </c>
       <c r="G7">
         <v>13.9</v>
@@ -1861,28 +1861,28 @@
         <v>36.2</v>
       </c>
       <c r="M7">
-        <v>1.389789</v>
+        <v>1.6677468</v>
       </c>
       <c r="N7">
-        <v>34.810211</v>
+        <v>34.5322532</v>
       </c>
       <c r="O7">
-        <v>8.702552750000001</v>
+        <v>8.6330633</v>
       </c>
       <c r="P7">
-        <v>26.10765825</v>
+        <v>25.8991899</v>
       </c>
       <c r="Q7">
-        <v>33.30765825</v>
+        <v>33.0991899</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1163378600103483</v>
+        <v>0.116907786161792</v>
       </c>
       <c r="T7">
-        <v>0.6821550171446661</v>
+        <v>0.6876666386136507</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.04711938287035</v>
+        <v>21.70593281905862</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1121568189920845</v>
+        <v>0.111906420974338</v>
       </c>
       <c r="C8">
-        <v>535.6577631263818</v>
+        <v>532.2336664552731</v>
       </c>
       <c r="D8">
-        <v>554.9137631263818</v>
+        <v>557.0156664552732</v>
       </c>
       <c r="E8">
-        <v>13.656</v>
+        <v>19.18199999999999</v>
       </c>
       <c r="F8">
-        <v>33.156</v>
+        <v>38.682</v>
       </c>
       <c r="G8">
         <v>13.9</v>
@@ -1943,28 +1943,28 @@
         <v>36.2</v>
       </c>
       <c r="M8">
-        <v>1.6677468</v>
+        <v>1.9457046</v>
       </c>
       <c r="N8">
-        <v>34.5322532</v>
+        <v>34.2542954</v>
       </c>
       <c r="O8">
-        <v>8.6330633</v>
+        <v>8.563573850000001</v>
       </c>
       <c r="P8">
-        <v>25.8991899</v>
+        <v>25.69072155</v>
       </c>
       <c r="Q8">
-        <v>33.0991899</v>
+        <v>32.89072154999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.116907786161792</v>
+        <v>0.1174899687896108</v>
       </c>
       <c r="T8">
-        <v>0.6876666386136507</v>
+        <v>0.693296789576592</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.70593281905863</v>
+        <v>18.60508527347883</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.111906420974338</v>
+        <v>0.1116560229565917</v>
       </c>
       <c r="C9">
-        <v>532.2336664552732</v>
+        <v>528.8255535136219</v>
       </c>
       <c r="D9">
-        <v>557.0156664552733</v>
+        <v>559.1335535136219</v>
       </c>
       <c r="E9">
-        <v>19.182</v>
+        <v>24.708</v>
       </c>
       <c r="F9">
-        <v>38.682</v>
+        <v>44.20800000000001</v>
       </c>
       <c r="G9">
         <v>13.9</v>
@@ -2025,28 +2025,28 @@
         <v>36.2</v>
       </c>
       <c r="M9">
-        <v>1.9457046</v>
+        <v>2.2236624</v>
       </c>
       <c r="N9">
-        <v>34.2542954</v>
+        <v>33.9763376</v>
       </c>
       <c r="O9">
-        <v>8.563573850000001</v>
+        <v>8.4940844</v>
       </c>
       <c r="P9">
-        <v>25.69072155</v>
+        <v>25.4822532</v>
       </c>
       <c r="Q9">
-        <v>32.89072154999999</v>
+        <v>32.6822532</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1174899687896108</v>
+        <v>0.1180848075615127</v>
       </c>
       <c r="T9">
-        <v>0.693296789576592</v>
+        <v>0.6990493351256842</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.60508527347882</v>
+        <v>16.27944961429397</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1116560229565917</v>
+        <v>0.1114056249388452</v>
       </c>
       <c r="C10">
-        <v>528.8255535136219</v>
+        <v>525.4336073174813</v>
       </c>
       <c r="D10">
-        <v>559.1335535136219</v>
+        <v>561.2676073174814</v>
       </c>
       <c r="E10">
-        <v>24.708</v>
+        <v>30.234</v>
       </c>
       <c r="F10">
-        <v>44.20800000000001</v>
+        <v>49.734</v>
       </c>
       <c r="G10">
         <v>13.9</v>
@@ -2107,28 +2107,28 @@
         <v>36.2</v>
       </c>
       <c r="M10">
-        <v>2.2236624</v>
+        <v>2.5016202</v>
       </c>
       <c r="N10">
-        <v>33.9763376</v>
+        <v>33.6983798</v>
       </c>
       <c r="O10">
-        <v>8.4940844</v>
+        <v>8.424594950000001</v>
       </c>
       <c r="P10">
-        <v>25.4822532</v>
+        <v>25.27378485000001</v>
       </c>
       <c r="Q10">
-        <v>32.6822532</v>
+        <v>32.47378485</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1180848075615127</v>
+        <v>0.1186927197130167</v>
       </c>
       <c r="T10">
-        <v>0.6990493351256842</v>
+        <v>0.7049283102472839</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.27944961429397</v>
+        <v>14.47062187937242</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1114056249388452</v>
+        <v>0.1111552269210988</v>
       </c>
       <c r="C11">
-        <v>525.4336073174813</v>
+        <v>522.0580136876904</v>
       </c>
       <c r="D11">
-        <v>561.2676073174814</v>
+        <v>563.4180136876904</v>
       </c>
       <c r="E11">
-        <v>30.234</v>
+        <v>35.75999999999999</v>
       </c>
       <c r="F11">
-        <v>49.734</v>
+        <v>55.26</v>
       </c>
       <c r="G11">
         <v>13.9</v>
@@ -2189,28 +2189,28 @@
         <v>36.2</v>
       </c>
       <c r="M11">
-        <v>2.5016202</v>
+        <v>2.779578</v>
       </c>
       <c r="N11">
-        <v>33.6983798</v>
+        <v>33.420422</v>
       </c>
       <c r="O11">
-        <v>8.424594950000001</v>
+        <v>8.355105500000001</v>
       </c>
       <c r="P11">
-        <v>25.27378485000001</v>
+        <v>25.0653165</v>
       </c>
       <c r="Q11">
-        <v>32.47378485</v>
+        <v>32.2653165</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1186927197130167</v>
+        <v>0.1193141410234431</v>
       </c>
       <c r="T11">
-        <v>0.7049283102472839</v>
+        <v>0.7109379292604747</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.47062187937242</v>
+        <v>13.02355969143518</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1111552269210988</v>
+        <v>0.1110285789033524</v>
       </c>
       <c r="C12">
-        <v>522.0580136876904</v>
+        <v>517.6259479078713</v>
       </c>
       <c r="D12">
-        <v>563.4180136876904</v>
+        <v>564.5119479078713</v>
       </c>
       <c r="E12">
-        <v>35.76000000000001</v>
+        <v>41.286</v>
       </c>
       <c r="F12">
-        <v>55.26000000000001</v>
+        <v>60.786</v>
       </c>
       <c r="G12">
         <v>13.9</v>
@@ -2271,45 +2271,45 @@
         <v>36.2</v>
       </c>
       <c r="M12">
-        <v>2.779578</v>
+        <v>3.1487148</v>
       </c>
       <c r="N12">
-        <v>33.420422</v>
+        <v>33.0512852</v>
       </c>
       <c r="O12">
-        <v>8.355105500000001</v>
+        <v>8.262821300000001</v>
       </c>
       <c r="P12">
-        <v>25.0653165</v>
+        <v>24.7884639</v>
       </c>
       <c r="Q12">
-        <v>32.2653165</v>
+        <v>31.9884639</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1193141410234431</v>
+        <v>0.1199495268576994</v>
       </c>
       <c r="T12">
-        <v>0.7109379292604747</v>
+        <v>0.7170825958919396</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.02355969143517</v>
+        <v>11.49675416776394</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1110285789033524</v>
+        <v>0.110789430885606</v>
       </c>
       <c r="C13">
-        <v>517.6259479078713</v>
+        <v>514.1772381917939</v>
       </c>
       <c r="D13">
-        <v>564.5119479078713</v>
+        <v>566.5892381917939</v>
       </c>
       <c r="E13">
-        <v>41.286</v>
+        <v>46.812</v>
       </c>
       <c r="F13">
-        <v>60.786</v>
+        <v>66.312</v>
       </c>
       <c r="G13">
         <v>13.9</v>
@@ -2353,28 +2353,28 @@
         <v>36.2</v>
       </c>
       <c r="M13">
-        <v>3.1487148</v>
+        <v>3.4349616</v>
       </c>
       <c r="N13">
-        <v>33.0512852</v>
+        <v>32.7650384</v>
       </c>
       <c r="O13">
-        <v>8.262821300000001</v>
+        <v>8.1912596</v>
       </c>
       <c r="P13">
-        <v>24.7884639</v>
+        <v>24.5737788</v>
       </c>
       <c r="Q13">
-        <v>31.9884639</v>
+        <v>31.7737788</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1199495268576994</v>
+        <v>0.1205993532790977</v>
       </c>
       <c r="T13">
-        <v>0.7170825958919396</v>
+        <v>0.7233669140377558</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.49675416776394</v>
+        <v>10.53869132045028</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.110789430885606</v>
+        <v>0.1107160328678596</v>
       </c>
       <c r="C14">
-        <v>514.1772381917939</v>
+        <v>509.2918584688273</v>
       </c>
       <c r="D14">
-        <v>566.5892381917939</v>
+        <v>567.2298584688274</v>
       </c>
       <c r="E14">
-        <v>46.812</v>
+        <v>52.33800000000001</v>
       </c>
       <c r="F14">
-        <v>66.312</v>
+        <v>71.83800000000001</v>
       </c>
       <c r="G14">
         <v>13.9</v>
@@ -2435,45 +2435,45 @@
         <v>36.2</v>
       </c>
       <c r="M14">
-        <v>3.4349616</v>
+        <v>3.843333</v>
       </c>
       <c r="N14">
-        <v>32.7650384</v>
+        <v>32.356667</v>
       </c>
       <c r="O14">
-        <v>8.1912596</v>
+        <v>8.08916675</v>
       </c>
       <c r="P14">
-        <v>24.5737788</v>
+        <v>24.26750025</v>
       </c>
       <c r="Q14">
-        <v>31.7737788</v>
+        <v>31.46750025</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1205993532790977</v>
+        <v>0.1212641182389191</v>
       </c>
       <c r="T14">
-        <v>0.7233669140377558</v>
+        <v>0.7297956992673839</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.53869132045028</v>
+        <v>9.41890801551674</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1107160328678596</v>
+        <v>0.1104896348501132</v>
       </c>
       <c r="C15">
-        <v>509.2918584688273</v>
+        <v>505.7510252712291</v>
       </c>
       <c r="D15">
-        <v>567.2298584688274</v>
+        <v>569.2150252712291</v>
       </c>
       <c r="E15">
-        <v>52.33800000000001</v>
+        <v>57.864</v>
       </c>
       <c r="F15">
-        <v>71.83800000000001</v>
+        <v>77.364</v>
       </c>
       <c r="G15">
         <v>13.9</v>
@@ -2517,28 +2517,28 @@
         <v>36.2</v>
       </c>
       <c r="M15">
-        <v>3.843333</v>
+        <v>4.138974</v>
       </c>
       <c r="N15">
-        <v>32.356667</v>
+        <v>32.06102600000001</v>
       </c>
       <c r="O15">
-        <v>8.08916675</v>
+        <v>8.015256500000001</v>
       </c>
       <c r="P15">
-        <v>24.26750025</v>
+        <v>24.04576950000001</v>
       </c>
       <c r="Q15">
-        <v>31.46750025</v>
+        <v>31.2457695</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1212641182389191</v>
+        <v>0.1219443428489688</v>
       </c>
       <c r="T15">
-        <v>0.7297956992673839</v>
+        <v>0.7363739911302591</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.41890801551674</v>
+        <v>8.74612887155126</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1104896348501132</v>
+        <v>0.1102632368323668</v>
       </c>
       <c r="C16">
-        <v>505.7510252712291</v>
+        <v>502.2241360780287</v>
       </c>
       <c r="D16">
-        <v>569.2150252712291</v>
+        <v>571.2141360780287</v>
       </c>
       <c r="E16">
-        <v>57.864</v>
+        <v>63.39000000000001</v>
       </c>
       <c r="F16">
-        <v>77.364</v>
+        <v>82.89000000000001</v>
       </c>
       <c r="G16">
         <v>13.9</v>
@@ -2599,28 +2599,28 @@
         <v>36.2</v>
       </c>
       <c r="M16">
-        <v>4.138974</v>
+        <v>4.434615000000001</v>
       </c>
       <c r="N16">
-        <v>32.06102600000001</v>
+        <v>31.765385</v>
       </c>
       <c r="O16">
-        <v>8.015256500000001</v>
+        <v>7.94134625</v>
       </c>
       <c r="P16">
-        <v>24.04576950000001</v>
+        <v>23.82403875</v>
       </c>
       <c r="Q16">
-        <v>31.2457695</v>
+        <v>31.02403875</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1219443428489688</v>
+        <v>0.1226405727439609</v>
       </c>
       <c r="T16">
-        <v>0.7363739911302591</v>
+        <v>0.7431070663310845</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.74612887155126</v>
+        <v>8.16305361344784</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1102632368323668</v>
+        <v>0.1100368388146204</v>
       </c>
       <c r="C17">
-        <v>502.2241360780287</v>
+        <v>498.7113383230833</v>
       </c>
       <c r="D17">
-        <v>571.2141360780287</v>
+        <v>573.2273383230834</v>
       </c>
       <c r="E17">
-        <v>63.39</v>
+        <v>68.91600000000001</v>
       </c>
       <c r="F17">
-        <v>82.89</v>
+        <v>88.41600000000001</v>
       </c>
       <c r="G17">
         <v>13.9</v>
@@ -2681,28 +2681,28 @@
         <v>36.2</v>
       </c>
       <c r="M17">
-        <v>4.434615</v>
+        <v>4.730256000000001</v>
       </c>
       <c r="N17">
-        <v>31.765385</v>
+        <v>31.469744</v>
       </c>
       <c r="O17">
-        <v>7.94134625</v>
+        <v>7.867436000000001</v>
       </c>
       <c r="P17">
-        <v>23.82403875</v>
+        <v>23.602308</v>
       </c>
       <c r="Q17">
-        <v>31.02403875</v>
+        <v>30.802308</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1226405727439609</v>
+        <v>0.1233533795412147</v>
       </c>
       <c r="T17">
-        <v>0.7431070663310845</v>
+        <v>0.7500004528462151</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.163053613447843</v>
+        <v>7.652862762607351</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1100368388146204</v>
+        <v>0.109912440796874</v>
       </c>
       <c r="C18">
-        <v>498.7113383230833</v>
+        <v>494.297577129142</v>
       </c>
       <c r="D18">
-        <v>573.2273383230834</v>
+        <v>574.3395771291421</v>
       </c>
       <c r="E18">
-        <v>68.91600000000001</v>
+        <v>74.44200000000001</v>
       </c>
       <c r="F18">
-        <v>88.41600000000001</v>
+        <v>93.94200000000001</v>
       </c>
       <c r="G18">
         <v>13.9</v>
@@ -2763,45 +2763,45 @@
         <v>36.2</v>
       </c>
       <c r="M18">
-        <v>4.730256000000001</v>
+        <v>5.101050600000001</v>
       </c>
       <c r="N18">
-        <v>31.469744</v>
+        <v>31.0989494</v>
       </c>
       <c r="O18">
-        <v>7.867436000000001</v>
+        <v>7.774737350000001</v>
       </c>
       <c r="P18">
-        <v>23.602308</v>
+        <v>23.32421205</v>
       </c>
       <c r="Q18">
-        <v>30.802308</v>
+        <v>30.52421205</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1233533795412147</v>
+        <v>0.1240833624058723</v>
       </c>
       <c r="T18">
-        <v>0.7500004528462151</v>
+        <v>0.7570599450605057</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.652862762607351</v>
+        <v>7.096577320758198</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.109912440796874</v>
+        <v>0.1096920427791276</v>
       </c>
       <c r="C19">
-        <v>494.297577129142</v>
+        <v>490.7527832200189</v>
       </c>
       <c r="D19">
-        <v>574.3395771291421</v>
+        <v>576.3207832200189</v>
       </c>
       <c r="E19">
-        <v>74.44200000000001</v>
+        <v>79.96800000000002</v>
       </c>
       <c r="F19">
-        <v>93.94200000000001</v>
+        <v>99.46800000000002</v>
       </c>
       <c r="G19">
         <v>13.9</v>
@@ -2845,28 +2845,28 @@
         <v>36.2</v>
       </c>
       <c r="M19">
-        <v>5.101050600000001</v>
+        <v>5.401112400000001</v>
       </c>
       <c r="N19">
-        <v>31.0989494</v>
+        <v>30.7988876</v>
       </c>
       <c r="O19">
-        <v>7.774737350000001</v>
+        <v>7.6997219</v>
       </c>
       <c r="P19">
-        <v>23.32421205</v>
+        <v>23.0991657</v>
       </c>
       <c r="Q19">
-        <v>30.52421205</v>
+        <v>30.2991657</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1240833624058723</v>
+        <v>0.1248311497306434</v>
       </c>
       <c r="T19">
-        <v>0.7570599450605057</v>
+        <v>0.7642916200117299</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.096577320758198</v>
+        <v>6.702323025160519</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1096920427791276</v>
+        <v>0.1094716447613812</v>
       </c>
       <c r="C20">
-        <v>490.7527832200188</v>
+        <v>487.2217051147456</v>
       </c>
       <c r="D20">
-        <v>576.3207832200188</v>
+        <v>578.3157051147457</v>
       </c>
       <c r="E20">
-        <v>79.968</v>
+        <v>85.494</v>
       </c>
       <c r="F20">
-        <v>99.468</v>
+        <v>104.994</v>
       </c>
       <c r="G20">
         <v>13.9</v>
@@ -2927,28 +2927,28 @@
         <v>36.2</v>
       </c>
       <c r="M20">
-        <v>5.401112400000001</v>
+        <v>5.701174200000001</v>
       </c>
       <c r="N20">
-        <v>30.7988876</v>
+        <v>30.4988258</v>
       </c>
       <c r="O20">
-        <v>7.6997219</v>
+        <v>7.624706450000001</v>
       </c>
       <c r="P20">
-        <v>23.0991657</v>
+        <v>22.87411935</v>
       </c>
       <c r="Q20">
-        <v>30.2991657</v>
+        <v>30.07411935</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1248311497306434</v>
+        <v>0.1255974009399767</v>
       </c>
       <c r="T20">
-        <v>0.7642916200117299</v>
+        <v>0.7717018548382932</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.70232302516052</v>
+        <v>6.349569181731019</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1094716447613812</v>
+        <v>0.1094012467436348</v>
       </c>
       <c r="C21">
-        <v>487.2217051147456</v>
+        <v>482.3358227438199</v>
       </c>
       <c r="D21">
-        <v>578.3157051147457</v>
+        <v>578.9558227438199</v>
       </c>
       <c r="E21">
-        <v>85.494</v>
+        <v>91.02000000000001</v>
       </c>
       <c r="F21">
-        <v>104.994</v>
+        <v>110.52</v>
       </c>
       <c r="G21">
         <v>13.9</v>
@@ -3009,45 +3009,45 @@
         <v>36.2</v>
       </c>
       <c r="M21">
-        <v>5.701174200000001</v>
+        <v>6.111756000000001</v>
       </c>
       <c r="N21">
-        <v>30.4988258</v>
+        <v>30.088244</v>
       </c>
       <c r="O21">
-        <v>7.624706450000001</v>
+        <v>7.522061000000001</v>
       </c>
       <c r="P21">
-        <v>22.87411935</v>
+        <v>22.566183</v>
       </c>
       <c r="Q21">
-        <v>30.07411935</v>
+        <v>29.766183</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1255974009399767</v>
+        <v>0.1263828084295434</v>
       </c>
       <c r="T21">
-        <v>0.7717018548382932</v>
+        <v>0.7792973455355204</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.349569181731019</v>
+        <v>5.923011324404967</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1094012467436348</v>
+        <v>0.1091883487258884</v>
       </c>
       <c r="C22">
-        <v>482.3358227438199</v>
+        <v>478.754321212425</v>
       </c>
       <c r="D22">
-        <v>578.9558227438199</v>
+        <v>580.9003212124251</v>
       </c>
       <c r="E22">
-        <v>91.02000000000001</v>
+        <v>96.54600000000002</v>
       </c>
       <c r="F22">
-        <v>110.52</v>
+        <v>116.046</v>
       </c>
       <c r="G22">
         <v>13.9</v>
@@ -3091,28 +3091,28 @@
         <v>36.2</v>
       </c>
       <c r="M22">
-        <v>6.111756000000001</v>
+        <v>6.417343800000001</v>
       </c>
       <c r="N22">
-        <v>30.088244</v>
+        <v>29.7826562</v>
       </c>
       <c r="O22">
-        <v>7.522061000000001</v>
+        <v>7.44566405</v>
       </c>
       <c r="P22">
-        <v>22.566183</v>
+        <v>22.33699215</v>
       </c>
       <c r="Q22">
-        <v>29.766183</v>
+        <v>29.53699215</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1263828084295434</v>
+        <v>0.1271880996530232</v>
       </c>
       <c r="T22">
-        <v>0.7792973455355204</v>
+        <v>0.7870851271364749</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.923011324404967</v>
+        <v>5.640963166099968</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1091883487258884</v>
+        <v>0.1089754507081419</v>
       </c>
       <c r="C23">
-        <v>478.7543212124251</v>
+        <v>475.1859254005728</v>
       </c>
       <c r="D23">
-        <v>580.9003212124251</v>
+        <v>582.8579254005729</v>
       </c>
       <c r="E23">
-        <v>96.54600000000001</v>
+        <v>102.072</v>
       </c>
       <c r="F23">
-        <v>116.046</v>
+        <v>121.572</v>
       </c>
       <c r="G23">
         <v>13.9</v>
@@ -3173,28 +3173,28 @@
         <v>36.2</v>
       </c>
       <c r="M23">
-        <v>6.4173438</v>
+        <v>6.722931600000001</v>
       </c>
       <c r="N23">
-        <v>29.7826562</v>
+        <v>29.4770684</v>
       </c>
       <c r="O23">
-        <v>7.44566405</v>
+        <v>7.3692671</v>
       </c>
       <c r="P23">
-        <v>22.33699215</v>
+        <v>22.1078013</v>
       </c>
       <c r="Q23">
-        <v>29.53699215</v>
+        <v>29.30780129999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1271880996530232</v>
+        <v>0.1280140393694127</v>
       </c>
       <c r="T23">
-        <v>0.7870851271364749</v>
+        <v>0.7950725954451463</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.640963166099968</v>
+        <v>5.38455574945906</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1089754507081419</v>
+        <v>0.1087625526903955</v>
       </c>
       <c r="C24">
-        <v>475.1859254005728</v>
+        <v>471.6307682530815</v>
       </c>
       <c r="D24">
-        <v>582.8579254005729</v>
+        <v>584.8287682530815</v>
       </c>
       <c r="E24">
-        <v>102.072</v>
+        <v>107.598</v>
       </c>
       <c r="F24">
-        <v>121.572</v>
+        <v>127.098</v>
       </c>
       <c r="G24">
         <v>13.9</v>
@@ -3255,28 +3255,28 @@
         <v>36.2</v>
       </c>
       <c r="M24">
-        <v>6.722931600000001</v>
+        <v>7.028519400000001</v>
       </c>
       <c r="N24">
-        <v>29.4770684</v>
+        <v>29.1714806</v>
       </c>
       <c r="O24">
-        <v>7.3692671</v>
+        <v>7.292870150000001</v>
       </c>
       <c r="P24">
-        <v>22.1078013</v>
+        <v>21.87861045</v>
       </c>
       <c r="Q24">
-        <v>29.30780129999999</v>
+        <v>29.07861045</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1280140393694127</v>
+        <v>0.1288614320654487</v>
       </c>
       <c r="T24">
-        <v>0.7950725954451463</v>
+        <v>0.8032675304631338</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.38455574945906</v>
+        <v>5.150444629917362</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1087625526903955</v>
+        <v>0.1085496546726491</v>
       </c>
       <c r="C25">
-        <v>471.6307682530815</v>
+        <v>468.0889845189985</v>
       </c>
       <c r="D25">
-        <v>584.8287682530815</v>
+        <v>586.8129845189985</v>
       </c>
       <c r="E25">
-        <v>107.598</v>
+        <v>113.124</v>
       </c>
       <c r="F25">
-        <v>127.098</v>
+        <v>132.624</v>
       </c>
       <c r="G25">
         <v>13.9</v>
@@ -3337,28 +3337,28 @@
         <v>36.2</v>
       </c>
       <c r="M25">
-        <v>7.028519400000001</v>
+        <v>7.334107200000002</v>
       </c>
       <c r="N25">
-        <v>29.1714806</v>
+        <v>28.8658928</v>
       </c>
       <c r="O25">
-        <v>7.292870150000001</v>
+        <v>7.2164732</v>
       </c>
       <c r="P25">
-        <v>21.87861045</v>
+        <v>21.6494196</v>
       </c>
       <c r="Q25">
-        <v>29.07861045</v>
+        <v>28.8494196</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1288614320654487</v>
+        <v>0.1297311245692752</v>
       </c>
       <c r="T25">
-        <v>0.8032675304631338</v>
+        <v>0.8116781216658052</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.150444629917362</v>
+        <v>4.935842770337471</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1085496546726491</v>
+        <v>0.1083367566549027</v>
       </c>
       <c r="C26">
-        <v>468.0889845189985</v>
+        <v>464.5607107823122</v>
       </c>
       <c r="D26">
-        <v>586.8129845189985</v>
+        <v>588.8107107823122</v>
       </c>
       <c r="E26">
-        <v>113.124</v>
+        <v>118.65</v>
       </c>
       <c r="F26">
-        <v>132.624</v>
+        <v>138.15</v>
       </c>
       <c r="G26">
         <v>13.9</v>
@@ -3419,28 +3419,28 @@
         <v>36.2</v>
       </c>
       <c r="M26">
-        <v>7.3341072</v>
+        <v>7.639695000000001</v>
       </c>
       <c r="N26">
-        <v>28.8658928</v>
+        <v>28.560305</v>
       </c>
       <c r="O26">
-        <v>7.216473200000001</v>
+        <v>7.140076250000001</v>
       </c>
       <c r="P26">
-        <v>21.6494196</v>
+        <v>21.42022875</v>
       </c>
       <c r="Q26">
-        <v>28.8494196</v>
+        <v>28.62022875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1297311245692752</v>
+        <v>0.1306240088732036</v>
       </c>
       <c r="T26">
-        <v>0.8116781216658052</v>
+        <v>0.8203129953005478</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.935842770337473</v>
+        <v>4.738409059523973</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1083367566549027</v>
+        <v>0.1081238586371563</v>
       </c>
       <c r="C27">
-        <v>464.5607107823122</v>
+        <v>461.0460854932911</v>
       </c>
       <c r="D27">
-        <v>588.8107107823122</v>
+        <v>590.8220854932912</v>
       </c>
       <c r="E27">
-        <v>118.65</v>
+        <v>124.176</v>
       </c>
       <c r="F27">
-        <v>138.15</v>
+        <v>143.676</v>
       </c>
       <c r="G27">
         <v>13.9</v>
@@ -3501,28 +3501,28 @@
         <v>36.2</v>
       </c>
       <c r="M27">
-        <v>7.639695000000001</v>
+        <v>7.945282800000001</v>
       </c>
       <c r="N27">
-        <v>28.560305</v>
+        <v>28.2547172</v>
       </c>
       <c r="O27">
-        <v>7.140076250000001</v>
+        <v>7.0636793</v>
       </c>
       <c r="P27">
-        <v>21.42022875</v>
+        <v>21.1910379</v>
       </c>
       <c r="Q27">
-        <v>28.62022875</v>
+        <v>28.3910379</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1306240088732036</v>
+        <v>0.1315410251853464</v>
       </c>
       <c r="T27">
-        <v>0.8203129953005478</v>
+        <v>0.8291812438983917</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.738409059523973</v>
+        <v>4.55616255723459</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1081238586371563</v>
+        <v>0.1084172106194099</v>
       </c>
       <c r="C28">
-        <v>461.0460854932911</v>
+        <v>452.7521750701952</v>
       </c>
       <c r="D28">
-        <v>590.8220854932912</v>
+        <v>588.0541750701952</v>
       </c>
       <c r="E28">
-        <v>124.176</v>
+        <v>129.702</v>
       </c>
       <c r="F28">
-        <v>143.676</v>
+        <v>149.202</v>
       </c>
       <c r="G28">
         <v>13.9</v>
@@ -3583,45 +3583,45 @@
         <v>36.2</v>
       </c>
       <c r="M28">
-        <v>7.945282800000001</v>
+        <v>8.623875600000002</v>
       </c>
       <c r="N28">
-        <v>28.2547172</v>
+        <v>27.5761244</v>
       </c>
       <c r="O28">
-        <v>7.0636793</v>
+        <v>6.8940311</v>
       </c>
       <c r="P28">
-        <v>21.1910379</v>
+        <v>20.6820933</v>
       </c>
       <c r="Q28">
-        <v>28.3910379</v>
+        <v>27.8820933</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1315410251853464</v>
+        <v>0.1324831652320684</v>
       </c>
       <c r="T28">
-        <v>0.8291812438983917</v>
+        <v>0.8382924582112448</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.55616255723459</v>
+        <v>4.197648676657627</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1084172106194099</v>
+        <v>0.1082230626016635</v>
       </c>
       <c r="C29">
-        <v>452.7521750701952</v>
+        <v>449.0551393609402</v>
       </c>
       <c r="D29">
-        <v>588.0541750701952</v>
+        <v>589.8831393609403</v>
       </c>
       <c r="E29">
-        <v>129.702</v>
+        <v>135.228</v>
       </c>
       <c r="F29">
-        <v>149.202</v>
+        <v>154.728</v>
       </c>
       <c r="G29">
         <v>13.9</v>
@@ -3665,28 +3665,28 @@
         <v>36.2</v>
       </c>
       <c r="M29">
-        <v>8.623875600000002</v>
+        <v>8.943278400000001</v>
       </c>
       <c r="N29">
-        <v>27.5761244</v>
+        <v>27.2567216</v>
       </c>
       <c r="O29">
-        <v>6.8940311</v>
+        <v>6.814180400000001</v>
       </c>
       <c r="P29">
-        <v>20.6820933</v>
+        <v>20.4425412</v>
       </c>
       <c r="Q29">
-        <v>27.8820933</v>
+        <v>27.6425412</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1324831652320684</v>
+        <v>0.1334514758356437</v>
       </c>
       <c r="T29">
-        <v>0.8382924582112448</v>
+        <v>0.8476567618105662</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.197648676657627</v>
+        <v>4.047732652491284</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1082230626016635</v>
+        <v>0.1087901645839171</v>
       </c>
       <c r="C30">
-        <v>449.0551393609402</v>
+        <v>438.2184071245781</v>
       </c>
       <c r="D30">
-        <v>589.8831393609403</v>
+        <v>584.5724071245781</v>
       </c>
       <c r="E30">
-        <v>135.228</v>
+        <v>140.754</v>
       </c>
       <c r="F30">
-        <v>154.728</v>
+        <v>160.254</v>
       </c>
       <c r="G30">
         <v>13.9</v>
@@ -3747,45 +3747,45 @@
         <v>36.2</v>
       </c>
       <c r="M30">
-        <v>8.943278400000001</v>
+        <v>9.823570200000001</v>
       </c>
       <c r="N30">
-        <v>27.2567216</v>
+        <v>26.3764298</v>
       </c>
       <c r="O30">
-        <v>6.814180400000001</v>
+        <v>6.594107450000001</v>
       </c>
       <c r="P30">
-        <v>20.4425412</v>
+        <v>19.78232235</v>
       </c>
       <c r="Q30">
-        <v>27.6425412</v>
+        <v>26.98232235</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1334514758356437</v>
+        <v>0.1344470627942494</v>
       </c>
       <c r="T30">
-        <v>0.8476567618105662</v>
+        <v>0.8572848486098682</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.047732652491284</v>
+        <v>3.685014639585922</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1087901645839171</v>
+        <v>0.1086222665661707</v>
       </c>
       <c r="C31">
-        <v>438.2184071245781</v>
+        <v>434.2547281573935</v>
       </c>
       <c r="D31">
-        <v>584.5724071245781</v>
+        <v>586.1347281573935</v>
       </c>
       <c r="E31">
-        <v>140.754</v>
+        <v>146.28</v>
       </c>
       <c r="F31">
-        <v>160.254</v>
+        <v>165.78</v>
       </c>
       <c r="G31">
         <v>13.9</v>
@@ -3829,28 +3829,28 @@
         <v>36.2</v>
       </c>
       <c r="M31">
-        <v>9.823570199999999</v>
+        <v>10.162314</v>
       </c>
       <c r="N31">
-        <v>26.3764298</v>
+        <v>26.037686</v>
       </c>
       <c r="O31">
-        <v>6.594107450000001</v>
+        <v>6.5094215</v>
       </c>
       <c r="P31">
-        <v>19.78232235</v>
+        <v>19.5282645</v>
       </c>
       <c r="Q31">
-        <v>26.98232235</v>
+        <v>26.72826449999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1344470627942494</v>
+        <v>0.1354710950945295</v>
       </c>
       <c r="T31">
-        <v>0.8572848486098682</v>
+        <v>0.8671880236034363</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.685014639585922</v>
+        <v>3.562180818266391</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1086222665661707</v>
+        <v>0.1091053685484243</v>
       </c>
       <c r="C32">
-        <v>434.2547281573935</v>
+        <v>424.2557607687919</v>
       </c>
       <c r="D32">
-        <v>586.1347281573935</v>
+        <v>581.661760768792</v>
       </c>
       <c r="E32">
-        <v>146.28</v>
+        <v>151.806</v>
       </c>
       <c r="F32">
-        <v>165.78</v>
+        <v>171.306</v>
       </c>
       <c r="G32">
         <v>13.9</v>
@@ -3911,45 +3911,45 @@
         <v>36.2</v>
       </c>
       <c r="M32">
-        <v>10.162314</v>
+        <v>10.9807146</v>
       </c>
       <c r="N32">
-        <v>26.037686</v>
+        <v>25.2192854</v>
       </c>
       <c r="O32">
-        <v>6.5094215</v>
+        <v>6.304821350000001</v>
       </c>
       <c r="P32">
-        <v>19.5282645</v>
+        <v>18.91446405</v>
       </c>
       <c r="Q32">
-        <v>26.72826449999999</v>
+        <v>26.11446405</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1354710950945295</v>
+        <v>0.1365248094904699</v>
       </c>
       <c r="T32">
-        <v>0.8671880236034363</v>
+        <v>0.8773782471475424</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.562180818266391</v>
+        <v>3.296688905838606</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1091053685484243</v>
+        <v>0.1089584705306779</v>
       </c>
       <c r="C33">
-        <v>424.2557607687919</v>
+        <v>420.0826269629521</v>
       </c>
       <c r="D33">
-        <v>581.661760768792</v>
+        <v>583.0146269629521</v>
       </c>
       <c r="E33">
-        <v>151.806</v>
+        <v>157.332</v>
       </c>
       <c r="F33">
-        <v>171.306</v>
+        <v>176.832</v>
       </c>
       <c r="G33">
         <v>13.9</v>
@@ -3993,28 +3993,28 @@
         <v>36.2</v>
       </c>
       <c r="M33">
-        <v>10.9807146</v>
+        <v>11.3349312</v>
       </c>
       <c r="N33">
-        <v>25.2192854</v>
+        <v>24.8650688</v>
       </c>
       <c r="O33">
-        <v>6.304821350000001</v>
+        <v>6.216267200000001</v>
       </c>
       <c r="P33">
-        <v>18.91446405</v>
+        <v>18.6488016</v>
       </c>
       <c r="Q33">
-        <v>26.11446405</v>
+        <v>25.8488016</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1365248094904699</v>
+        <v>0.137609515486291</v>
       </c>
       <c r="T33">
-        <v>0.8773782471475424</v>
+        <v>0.8878681831488282</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.296688905838606</v>
+        <v>3.193667377531149</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1089584705306779</v>
+        <v>0.1088115725129314</v>
       </c>
       <c r="C34">
-        <v>420.0826269629521</v>
+        <v>415.9158009940468</v>
       </c>
       <c r="D34">
-        <v>583.0146269629521</v>
+        <v>584.3738009940469</v>
       </c>
       <c r="E34">
-        <v>157.332</v>
+        <v>162.858</v>
       </c>
       <c r="F34">
-        <v>176.832</v>
+        <v>182.358</v>
       </c>
       <c r="G34">
         <v>13.9</v>
@@ -4075,28 +4075,28 @@
         <v>36.2</v>
       </c>
       <c r="M34">
-        <v>11.3349312</v>
+        <v>11.6891478</v>
       </c>
       <c r="N34">
-        <v>24.8650688</v>
+        <v>24.5108522</v>
       </c>
       <c r="O34">
-        <v>6.216267200000001</v>
+        <v>6.127713050000001</v>
       </c>
       <c r="P34">
-        <v>18.6488016</v>
+        <v>18.38313915</v>
       </c>
       <c r="Q34">
-        <v>25.8488016</v>
+        <v>25.58313915</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.137609515486291</v>
+        <v>0.1387266007655693</v>
       </c>
       <c r="T34">
-        <v>0.8878681831488282</v>
+        <v>0.8986712515680629</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.193667377531149</v>
+        <v>3.096889578212023</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1088115725129314</v>
+        <v>0.108664674495185</v>
       </c>
       <c r="C35">
-        <v>415.9158009940468</v>
+        <v>411.7553270812858</v>
       </c>
       <c r="D35">
-        <v>584.3738009940469</v>
+        <v>585.7393270812859</v>
       </c>
       <c r="E35">
-        <v>162.858</v>
+        <v>168.384</v>
       </c>
       <c r="F35">
-        <v>182.358</v>
+        <v>187.884</v>
       </c>
       <c r="G35">
         <v>13.9</v>
@@ -4157,28 +4157,28 @@
         <v>36.2</v>
       </c>
       <c r="M35">
-        <v>11.6891478</v>
+        <v>12.0433644</v>
       </c>
       <c r="N35">
-        <v>24.5108522</v>
+        <v>24.1566356</v>
       </c>
       <c r="O35">
-        <v>6.127713050000001</v>
+        <v>6.0391589</v>
       </c>
       <c r="P35">
-        <v>18.38313915</v>
+        <v>18.1174767</v>
       </c>
       <c r="Q35">
-        <v>25.58313915</v>
+        <v>25.3174767</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1387266007655693</v>
+        <v>0.1398775371139167</v>
       </c>
       <c r="T35">
-        <v>0.8986712515680629</v>
+        <v>0.9098016856969713</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.096889578212023</v>
+        <v>3.005804590617552</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.108664674495185</v>
+        <v>0.1105652764774386</v>
       </c>
       <c r="C36">
-        <v>411.7553270812858</v>
+        <v>389.0402191721673</v>
       </c>
       <c r="D36">
-        <v>585.7393270812859</v>
+        <v>568.5502191721673</v>
       </c>
       <c r="E36">
-        <v>168.384</v>
+        <v>173.91</v>
       </c>
       <c r="F36">
-        <v>187.884</v>
+        <v>193.41</v>
       </c>
       <c r="G36">
         <v>13.9</v>
@@ -4239,45 +4239,45 @@
         <v>36.2</v>
       </c>
       <c r="M36">
-        <v>12.0433644</v>
+        <v>13.906179</v>
       </c>
       <c r="N36">
-        <v>24.1566356</v>
+        <v>22.293821</v>
       </c>
       <c r="O36">
-        <v>6.0391589</v>
+        <v>5.57345525</v>
       </c>
       <c r="P36">
-        <v>18.1174767</v>
+        <v>16.72036575</v>
       </c>
       <c r="Q36">
-        <v>25.3174767</v>
+        <v>23.92036574999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1398775371139167</v>
+        <v>0.1410638868883672</v>
       </c>
       <c r="T36">
-        <v>0.9098016856969713</v>
+        <v>0.9212745947221538</v>
       </c>
       <c r="U36">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.005804590617552</v>
+        <v>2.603159358152947</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1105652764774386</v>
+        <v>0.1104768784596922</v>
       </c>
       <c r="C37">
-        <v>389.0402191721673</v>
+        <v>384.2912930440215</v>
       </c>
       <c r="D37">
-        <v>568.5502191721673</v>
+        <v>569.3272930440215</v>
       </c>
       <c r="E37">
-        <v>173.91</v>
+        <v>179.436</v>
       </c>
       <c r="F37">
-        <v>193.41</v>
+        <v>198.936</v>
       </c>
       <c r="G37">
         <v>13.9</v>
@@ -4321,28 +4321,28 @@
         <v>36.2</v>
       </c>
       <c r="M37">
-        <v>13.906179</v>
+        <v>14.3034984</v>
       </c>
       <c r="N37">
-        <v>22.293821</v>
+        <v>21.8965016</v>
       </c>
       <c r="O37">
-        <v>5.57345525</v>
+        <v>5.4741254</v>
       </c>
       <c r="P37">
-        <v>16.72036575</v>
+        <v>16.4223762</v>
       </c>
       <c r="Q37">
-        <v>23.92036574999999</v>
+        <v>23.6223762</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1410638868883672</v>
+        <v>0.1422873100932691</v>
       </c>
       <c r="T37">
-        <v>0.9212745947221538</v>
+        <v>0.9331060321543732</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.603159358152947</v>
+        <v>2.530849375982032</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1104768784596922</v>
+        <v>0.1114707304419458</v>
       </c>
       <c r="C38">
-        <v>384.2912930440214</v>
+        <v>370.1491705350281</v>
       </c>
       <c r="D38">
-        <v>569.3272930440214</v>
+        <v>560.7111705350281</v>
       </c>
       <c r="E38">
-        <v>179.436</v>
+        <v>184.962</v>
       </c>
       <c r="F38">
-        <v>198.936</v>
+        <v>204.462</v>
       </c>
       <c r="G38">
         <v>13.9</v>
@@ -4403,45 +4403,45 @@
         <v>36.2</v>
       </c>
       <c r="M38">
-        <v>14.3034984</v>
+        <v>15.4982196</v>
       </c>
       <c r="N38">
-        <v>21.8965016</v>
+        <v>20.7017804</v>
       </c>
       <c r="O38">
-        <v>5.4741254</v>
+        <v>5.1754451</v>
       </c>
       <c r="P38">
-        <v>16.4223762</v>
+        <v>15.5263353</v>
       </c>
       <c r="Q38">
-        <v>23.6223762</v>
+        <v>22.7263353</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1422873100932691</v>
+        <v>0.1435495721300727</v>
       </c>
       <c r="T38">
-        <v>0.9331060321543732</v>
+        <v>0.945313070774917</v>
       </c>
       <c r="U38">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.530849375982032</v>
+        <v>2.335752166010088</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1114707304419458</v>
+        <v>0.1114115824241994</v>
       </c>
       <c r="C39">
-        <v>370.1491705350281</v>
+        <v>365.1286446150618</v>
       </c>
       <c r="D39">
-        <v>560.7111705350281</v>
+        <v>561.2166446150618</v>
       </c>
       <c r="E39">
-        <v>184.962</v>
+        <v>190.488</v>
       </c>
       <c r="F39">
-        <v>204.462</v>
+        <v>209.988</v>
       </c>
       <c r="G39">
         <v>13.9</v>
@@ -4485,28 +4485,28 @@
         <v>36.2</v>
       </c>
       <c r="M39">
-        <v>15.4982196</v>
+        <v>15.9170904</v>
       </c>
       <c r="N39">
-        <v>20.7017804</v>
+        <v>20.2829096</v>
       </c>
       <c r="O39">
-        <v>5.1754451</v>
+        <v>5.070727400000001</v>
       </c>
       <c r="P39">
-        <v>15.5263353</v>
+        <v>15.2121822</v>
       </c>
       <c r="Q39">
-        <v>22.7263353</v>
+        <v>22.4121822</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1435495721300727</v>
+        <v>0.1448525522970958</v>
       </c>
       <c r="T39">
-        <v>0.945313070774917</v>
+        <v>0.9579138848348333</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.335752166010088</v>
+        <v>2.274285003746665</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1114115824241994</v>
+        <v>0.111352434406453</v>
       </c>
       <c r="C40">
-        <v>365.1286446150618</v>
+        <v>360.1090308744865</v>
       </c>
       <c r="D40">
-        <v>561.2166446150618</v>
+        <v>561.7230308744865</v>
       </c>
       <c r="E40">
-        <v>190.488</v>
+        <v>196.014</v>
       </c>
       <c r="F40">
-        <v>209.988</v>
+        <v>215.514</v>
       </c>
       <c r="G40">
         <v>13.9</v>
@@ -4567,28 +4567,28 @@
         <v>36.2</v>
       </c>
       <c r="M40">
-        <v>15.9170904</v>
+        <v>16.3359612</v>
       </c>
       <c r="N40">
-        <v>20.2829096</v>
+        <v>19.8640388</v>
       </c>
       <c r="O40">
-        <v>5.070727400000001</v>
+        <v>4.9660097</v>
       </c>
       <c r="P40">
-        <v>15.2121822</v>
+        <v>14.8980291</v>
       </c>
       <c r="Q40">
-        <v>22.4121822</v>
+        <v>22.09802909999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1448525522970958</v>
+        <v>0.1461982531253328</v>
       </c>
       <c r="T40">
-        <v>0.9579138848348333</v>
+        <v>0.9709278403393369</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.274285003746665</v>
+        <v>2.215970003650596</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.111352434406453</v>
+        <v>0.1112932863887066</v>
       </c>
       <c r="C41">
-        <v>360.1090308744865</v>
+        <v>355.090331784713</v>
       </c>
       <c r="D41">
-        <v>561.7230308744865</v>
+        <v>562.230331784713</v>
       </c>
       <c r="E41">
-        <v>196.014</v>
+        <v>201.54</v>
       </c>
       <c r="F41">
-        <v>215.514</v>
+        <v>221.04</v>
       </c>
       <c r="G41">
         <v>13.9</v>
@@ -4649,28 +4649,28 @@
         <v>36.2</v>
       </c>
       <c r="M41">
-        <v>16.3359612</v>
+        <v>16.754832</v>
       </c>
       <c r="N41">
-        <v>19.8640388</v>
+        <v>19.445168</v>
       </c>
       <c r="O41">
-        <v>4.9660097</v>
+        <v>4.861292</v>
       </c>
       <c r="P41">
-        <v>14.8980291</v>
+        <v>14.583876</v>
       </c>
       <c r="Q41">
-        <v>22.09802909999999</v>
+        <v>21.783876</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1461982531253328</v>
+        <v>0.1475888106478443</v>
       </c>
       <c r="T41">
-        <v>0.9709278403393369</v>
+        <v>0.9843755943606574</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.215970003650596</v>
+        <v>2.160570753559331</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1112932863887066</v>
+        <v>0.1112341383709602</v>
       </c>
       <c r="C42">
-        <v>355.090331784713</v>
+        <v>350.0725498260886</v>
       </c>
       <c r="D42">
-        <v>562.230331784713</v>
+        <v>562.7385498260886</v>
       </c>
       <c r="E42">
-        <v>201.54</v>
+        <v>207.066</v>
       </c>
       <c r="F42">
-        <v>221.04</v>
+        <v>226.566</v>
       </c>
       <c r="G42">
         <v>13.9</v>
@@ -4731,28 +4731,28 @@
         <v>36.2</v>
       </c>
       <c r="M42">
-        <v>16.754832</v>
+        <v>17.1737028</v>
       </c>
       <c r="N42">
-        <v>19.445168</v>
+        <v>19.0262972</v>
       </c>
       <c r="O42">
-        <v>4.861292</v>
+        <v>4.7565743</v>
       </c>
       <c r="P42">
-        <v>14.583876</v>
+        <v>14.2697229</v>
       </c>
       <c r="Q42">
-        <v>21.783876</v>
+        <v>21.46972289999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1475888106478443</v>
+        <v>0.1490265057134919</v>
       </c>
       <c r="T42">
-        <v>0.9843755943606574</v>
+        <v>0.9982792044504972</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.160570753559331</v>
+        <v>2.107873905911543</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1112341383709602</v>
+        <v>0.1111749903532138</v>
       </c>
       <c r="C43">
-        <v>350.0725498260886</v>
+        <v>345.0556874879354</v>
       </c>
       <c r="D43">
-        <v>562.7385498260886</v>
+        <v>563.2476874879354</v>
       </c>
       <c r="E43">
-        <v>207.066</v>
+        <v>212.592</v>
       </c>
       <c r="F43">
-        <v>226.566</v>
+        <v>232.092</v>
       </c>
       <c r="G43">
         <v>13.9</v>
@@ -4813,28 +4813,28 @@
         <v>36.2</v>
       </c>
       <c r="M43">
-        <v>17.1737028</v>
+        <v>17.59257360000001</v>
       </c>
       <c r="N43">
-        <v>19.0262972</v>
+        <v>18.6074264</v>
       </c>
       <c r="O43">
-        <v>4.7565743</v>
+        <v>4.651856599999999</v>
       </c>
       <c r="P43">
-        <v>14.2697229</v>
+        <v>13.9555698</v>
       </c>
       <c r="Q43">
-        <v>21.46972289999999</v>
+        <v>21.15556979999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1490265057134919</v>
+        <v>0.1505137764710583</v>
       </c>
       <c r="T43">
-        <v>0.9982792044504972</v>
+        <v>1.012662249371021</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.107873905911543</v>
+        <v>2.057686431961268</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1111749903532138</v>
+        <v>0.1111158423354674</v>
       </c>
       <c r="C44">
-        <v>345.0556874879354</v>
+        <v>340.0397472685939</v>
       </c>
       <c r="D44">
-        <v>563.2476874879354</v>
+        <v>563.7577472685939</v>
       </c>
       <c r="E44">
-        <v>212.592</v>
+        <v>218.118</v>
       </c>
       <c r="F44">
-        <v>232.092</v>
+        <v>237.618</v>
       </c>
       <c r="G44">
         <v>13.9</v>
@@ -4895,28 +4895,28 @@
         <v>36.2</v>
       </c>
       <c r="M44">
-        <v>17.5925736</v>
+        <v>18.0114444</v>
       </c>
       <c r="N44">
-        <v>18.6074264</v>
+        <v>18.1885556</v>
       </c>
       <c r="O44">
-        <v>4.6518566</v>
+        <v>4.5471389</v>
       </c>
       <c r="P44">
-        <v>13.9555698</v>
+        <v>13.6414167</v>
       </c>
       <c r="Q44">
-        <v>21.15556979999999</v>
+        <v>20.8414167</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1505137764710583</v>
+        <v>0.1520532321674866</v>
       </c>
       <c r="T44">
-        <v>1.012662249371021</v>
+        <v>1.02754996253437</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.057686431961268</v>
+        <v>2.009833259124959</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1111158423354674</v>
+        <v>0.115742694317721</v>
       </c>
       <c r="C45">
-        <v>340.0397472685939</v>
+        <v>297.2200216564304</v>
       </c>
       <c r="D45">
-        <v>563.7577472685939</v>
+        <v>526.4640216564304</v>
       </c>
       <c r="E45">
-        <v>218.118</v>
+        <v>223.644</v>
       </c>
       <c r="F45">
-        <v>237.618</v>
+        <v>243.144</v>
       </c>
       <c r="G45">
         <v>13.9</v>
@@ -4977,45 +4977,45 @@
         <v>36.2</v>
       </c>
       <c r="M45">
-        <v>18.0114444</v>
+        <v>21.88296</v>
       </c>
       <c r="N45">
-        <v>18.1885556</v>
+        <v>14.31704</v>
       </c>
       <c r="O45">
-        <v>4.5471389</v>
+        <v>3.579260000000001</v>
       </c>
       <c r="P45">
-        <v>13.6414167</v>
+        <v>10.73778</v>
       </c>
       <c r="Q45">
-        <v>20.8414167</v>
+        <v>17.93778</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1520532321674866</v>
+        <v>0.1536476684245018</v>
       </c>
       <c r="T45">
-        <v>1.02754996253437</v>
+        <v>1.042969379739268</v>
       </c>
       <c r="U45">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.009833259124959</v>
+        <v>1.654255183028256</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.115742694317721</v>
+        <v>0.1157900462999746</v>
       </c>
       <c r="C46">
-        <v>297.2200216564304</v>
+        <v>291.3378407946007</v>
       </c>
       <c r="D46">
-        <v>526.4640216564304</v>
+        <v>526.1078407946007</v>
       </c>
       <c r="E46">
-        <v>223.644</v>
+        <v>229.17</v>
       </c>
       <c r="F46">
-        <v>243.144</v>
+        <v>248.67</v>
       </c>
       <c r="G46">
         <v>13.9</v>
@@ -5059,28 +5059,28 @@
         <v>36.2</v>
       </c>
       <c r="M46">
-        <v>21.88296</v>
+        <v>22.3803</v>
       </c>
       <c r="N46">
-        <v>14.31704</v>
+        <v>13.8197</v>
       </c>
       <c r="O46">
-        <v>3.579260000000001</v>
+        <v>3.454925</v>
       </c>
       <c r="P46">
-        <v>10.73778</v>
+        <v>10.364775</v>
       </c>
       <c r="Q46">
-        <v>17.93778</v>
+        <v>17.564775</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1536476684245018</v>
+        <v>0.1553000841817719</v>
       </c>
       <c r="T46">
-        <v>1.042969379739268</v>
+        <v>1.058949503024343</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.654255183028256</v>
+        <v>1.617493956738739</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1157900462999746</v>
+        <v>0.1158373982822282</v>
       </c>
       <c r="C47">
-        <v>291.3378407946007</v>
+        <v>285.4561415574531</v>
       </c>
       <c r="D47">
-        <v>526.1078407946007</v>
+        <v>525.7521415574531</v>
       </c>
       <c r="E47">
-        <v>229.17</v>
+        <v>234.696</v>
       </c>
       <c r="F47">
-        <v>248.67</v>
+        <v>254.196</v>
       </c>
       <c r="G47">
         <v>13.9</v>
@@ -5141,28 +5141,28 @@
         <v>36.2</v>
       </c>
       <c r="M47">
-        <v>22.3803</v>
+        <v>22.87764</v>
       </c>
       <c r="N47">
-        <v>13.8197</v>
+        <v>13.32236</v>
       </c>
       <c r="O47">
-        <v>3.454925</v>
+        <v>3.33059</v>
       </c>
       <c r="P47">
-        <v>10.364775</v>
+        <v>9.991769999999999</v>
       </c>
       <c r="Q47">
-        <v>17.564775</v>
+        <v>17.19176999999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1553000841817719</v>
+        <v>0.1570137005226447</v>
       </c>
       <c r="T47">
-        <v>1.058949503024343</v>
+        <v>1.075521482727385</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.617493956738739</v>
+        <v>1.582331044635723</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1158373982822282</v>
+        <v>0.1158847502644818</v>
       </c>
       <c r="C48">
-        <v>285.4561415574531</v>
+        <v>279.5749229687748</v>
       </c>
       <c r="D48">
-        <v>525.7521415574531</v>
+        <v>525.3969229687749</v>
       </c>
       <c r="E48">
-        <v>234.696</v>
+        <v>240.222</v>
       </c>
       <c r="F48">
-        <v>254.196</v>
+        <v>259.722</v>
       </c>
       <c r="G48">
         <v>13.9</v>
@@ -5223,28 +5223,28 @@
         <v>36.2</v>
       </c>
       <c r="M48">
-        <v>22.87764</v>
+        <v>23.37498</v>
       </c>
       <c r="N48">
-        <v>13.32236</v>
+        <v>12.82502</v>
       </c>
       <c r="O48">
-        <v>3.33059</v>
+        <v>3.206255000000001</v>
       </c>
       <c r="P48">
-        <v>9.991769999999999</v>
+        <v>9.618765000000002</v>
       </c>
       <c r="Q48">
-        <v>17.19176999999999</v>
+        <v>16.818765</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1570137005226447</v>
+        <v>0.1587919816310976</v>
       </c>
       <c r="T48">
-        <v>1.075521482727385</v>
+        <v>1.092718820155069</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.582331044635723</v>
+        <v>1.54866442666475</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1158847502644818</v>
+        <v>0.1159321022467353</v>
       </c>
       <c r="C49">
-        <v>279.5749229687748</v>
+        <v>273.6941840549894</v>
       </c>
       <c r="D49">
-        <v>525.3969229687749</v>
+        <v>525.0421840549894</v>
       </c>
       <c r="E49">
-        <v>240.222</v>
+        <v>245.748</v>
       </c>
       <c r="F49">
-        <v>259.722</v>
+        <v>265.248</v>
       </c>
       <c r="G49">
         <v>13.9</v>
@@ -5305,28 +5305,28 @@
         <v>36.2</v>
       </c>
       <c r="M49">
-        <v>23.37498</v>
+        <v>23.87232</v>
       </c>
       <c r="N49">
-        <v>12.82502</v>
+        <v>12.32768</v>
       </c>
       <c r="O49">
-        <v>3.206255000000001</v>
+        <v>3.08192</v>
       </c>
       <c r="P49">
-        <v>9.618765000000002</v>
+        <v>9.245760000000001</v>
       </c>
       <c r="Q49">
-        <v>16.818765</v>
+        <v>16.44576</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1587919816310976</v>
+        <v>0.1606386581667987</v>
       </c>
       <c r="T49">
-        <v>1.092718820155069</v>
+        <v>1.110577593637665</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.54866442666475</v>
+        <v>1.516400584442568</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1159321022467353</v>
+        <v>0.1392016529522238</v>
       </c>
       <c r="C50">
-        <v>273.6941840549894</v>
+        <v>137.362193601722</v>
       </c>
       <c r="D50">
-        <v>525.0421840549894</v>
+        <v>394.2361936017221</v>
       </c>
       <c r="E50">
-        <v>245.748</v>
+        <v>251.274</v>
       </c>
       <c r="F50">
-        <v>265.248</v>
+        <v>270.774</v>
       </c>
       <c r="G50">
         <v>13.9</v>
@@ -5387,45 +5387,45 @@
         <v>36.2</v>
       </c>
       <c r="M50">
-        <v>23.87232</v>
+        <v>39.7496232</v>
       </c>
       <c r="N50">
-        <v>12.32768</v>
+        <v>-3.549623199999999</v>
       </c>
       <c r="O50">
-        <v>3.081920000000001</v>
+        <v>-0.8874057999999998</v>
       </c>
       <c r="P50">
-        <v>9.245760000000004</v>
+        <v>-2.662217399999999</v>
       </c>
       <c r="Q50">
-        <v>16.44576</v>
+        <v>4.537782599999996</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1606386581667987</v>
+        <v>0.1640132926749088</v>
       </c>
       <c r="T50">
-        <v>1.110577593637665</v>
+        <v>1.143212888504834</v>
       </c>
       <c r="U50">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.25</v>
+        <v>0.2276751141630948</v>
       </c>
       <c r="W50">
-        <v>0.0675</v>
+        <v>0.1133772932408577</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.516400584442568</v>
+        <v>0.9107004566523791</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1392016529522238</v>
+        <v>0.1402116529522238</v>
       </c>
       <c r="C51">
-        <v>137.362193601722</v>
+        <v>127.6187210431256</v>
       </c>
       <c r="D51">
-        <v>394.2361936017221</v>
+        <v>390.0187210431256</v>
       </c>
       <c r="E51">
-        <v>251.274</v>
+        <v>256.8</v>
       </c>
       <c r="F51">
-        <v>270.774</v>
+        <v>276.3</v>
       </c>
       <c r="G51">
         <v>13.9</v>
@@ -5469,37 +5469,37 @@
         <v>36.2</v>
       </c>
       <c r="M51">
-        <v>39.7496232</v>
+        <v>40.56084000000001</v>
       </c>
       <c r="N51">
-        <v>-3.549623199999999</v>
+        <v>-4.360840000000003</v>
       </c>
       <c r="O51">
-        <v>-0.8874057999999998</v>
+        <v>-1.090210000000001</v>
       </c>
       <c r="P51">
-        <v>-2.662217399999999</v>
+        <v>-3.270630000000002</v>
       </c>
       <c r="Q51">
-        <v>4.537782599999996</v>
+        <v>3.929369999999993</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1640132926749088</v>
+        <v>0.166377558528407</v>
       </c>
       <c r="T51">
-        <v>1.143212888504834</v>
+        <v>1.166077146274931</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2276751141630948</v>
+        <v>0.2231216118798328</v>
       </c>
       <c r="W51">
-        <v>0.1133772932408577</v>
+        <v>0.1140457473760405</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9107004566523791</v>
+        <v>0.8924864475193314</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1402116529522238</v>
+        <v>0.1412216529522238</v>
       </c>
       <c r="C52">
-        <v>127.6187210431256</v>
+        <v>117.9645290021557</v>
       </c>
       <c r="D52">
-        <v>390.0187210431256</v>
+        <v>385.8905290021557</v>
       </c>
       <c r="E52">
-        <v>256.8</v>
+        <v>262.326</v>
       </c>
       <c r="F52">
-        <v>276.3</v>
+        <v>281.826</v>
       </c>
       <c r="G52">
         <v>13.9</v>
@@ -5551,37 +5551,37 @@
         <v>36.2</v>
       </c>
       <c r="M52">
-        <v>40.56084000000001</v>
+        <v>41.37205680000001</v>
       </c>
       <c r="N52">
-        <v>-4.360840000000003</v>
+        <v>-5.172056800000007</v>
       </c>
       <c r="O52">
-        <v>-1.090210000000001</v>
+        <v>-1.293014200000002</v>
       </c>
       <c r="P52">
-        <v>-3.270630000000002</v>
+        <v>-3.879042600000005</v>
       </c>
       <c r="Q52">
-        <v>3.929369999999993</v>
+        <v>3.32095739999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.166377558528407</v>
+        <v>0.1688383250289868</v>
       </c>
       <c r="T52">
-        <v>1.166077146274931</v>
+        <v>1.189874639056052</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2231216118798328</v>
+        <v>0.2187466783135616</v>
       </c>
       <c r="W52">
-        <v>0.1140457473760405</v>
+        <v>0.1146879876235692</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8924864475193314</v>
+        <v>0.8749867132542464</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1412216529522238</v>
+        <v>0.1422316529522238</v>
       </c>
       <c r="C53">
-        <v>117.9645290021557</v>
+        <v>108.3968121761953</v>
       </c>
       <c r="D53">
-        <v>385.8905290021557</v>
+        <v>381.8488121761954</v>
       </c>
       <c r="E53">
-        <v>262.326</v>
+        <v>267.852</v>
       </c>
       <c r="F53">
-        <v>281.826</v>
+        <v>287.352</v>
       </c>
       <c r="G53">
         <v>13.9</v>
@@ -5633,37 +5633,37 @@
         <v>36.2</v>
       </c>
       <c r="M53">
-        <v>41.37205680000001</v>
+        <v>42.18327360000001</v>
       </c>
       <c r="N53">
-        <v>-5.172056800000007</v>
+        <v>-5.983273600000004</v>
       </c>
       <c r="O53">
-        <v>-1.293014200000002</v>
+        <v>-1.495818400000001</v>
       </c>
       <c r="P53">
-        <v>-3.879042600000005</v>
+        <v>-4.487455200000003</v>
       </c>
       <c r="Q53">
-        <v>3.32095739999999</v>
+        <v>2.712544799999993</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1688383250289868</v>
+        <v>0.1714016234670907</v>
       </c>
       <c r="T53">
-        <v>1.189874639056052</v>
+        <v>1.214663694036386</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.2187466783135616</v>
+        <v>0.2145400114229162</v>
       </c>
       <c r="W53">
-        <v>0.1146879876235692</v>
+        <v>0.1153055263231159</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8749867132542464</v>
+        <v>0.8581600456916648</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1422316529522238</v>
+        <v>0.1432416529522238</v>
       </c>
       <c r="C54">
-        <v>108.3968121761953</v>
+        <v>98.91288157246203</v>
       </c>
       <c r="D54">
-        <v>381.8488121761954</v>
+        <v>377.8908815724621</v>
       </c>
       <c r="E54">
-        <v>267.852</v>
+        <v>273.378</v>
       </c>
       <c r="F54">
-        <v>287.352</v>
+        <v>292.878</v>
       </c>
       <c r="G54">
         <v>13.9</v>
@@ -5715,37 +5715,37 @@
         <v>36.2</v>
       </c>
       <c r="M54">
-        <v>42.18327360000001</v>
+        <v>42.99449040000001</v>
       </c>
       <c r="N54">
-        <v>-5.983273600000004</v>
+        <v>-6.794490400000008</v>
       </c>
       <c r="O54">
-        <v>-1.495818400000001</v>
+        <v>-1.698622600000002</v>
       </c>
       <c r="P54">
-        <v>-4.487455200000003</v>
+        <v>-5.095867800000006</v>
       </c>
       <c r="Q54">
-        <v>2.712544799999993</v>
+        <v>2.10413219999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1714016234670907</v>
+        <v>0.1740739984344756</v>
       </c>
       <c r="T54">
-        <v>1.214663694036386</v>
+        <v>1.240507602420139</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2145400114229162</v>
+        <v>0.2104920866790876</v>
       </c>
       <c r="W54">
-        <v>0.1153055263231159</v>
+        <v>0.11589976167551</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8581600456916648</v>
+        <v>0.8419683467163503</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1432416529522238</v>
+        <v>0.1442516529522238</v>
       </c>
       <c r="C55">
-        <v>98.91288157246203</v>
+        <v>89.51015854198727</v>
       </c>
       <c r="D55">
-        <v>377.8908815724621</v>
+        <v>374.0141585419873</v>
       </c>
       <c r="E55">
-        <v>273.378</v>
+        <v>278.9040000000001</v>
       </c>
       <c r="F55">
-        <v>292.878</v>
+        <v>298.4040000000001</v>
       </c>
       <c r="G55">
         <v>13.9</v>
@@ -5797,37 +5797,37 @@
         <v>36.2</v>
       </c>
       <c r="M55">
-        <v>42.99449040000001</v>
+        <v>43.80570720000001</v>
       </c>
       <c r="N55">
-        <v>-6.794490400000008</v>
+        <v>-7.605707200000012</v>
       </c>
       <c r="O55">
-        <v>-1.698622600000002</v>
+        <v>-1.901426800000003</v>
       </c>
       <c r="P55">
-        <v>-5.095867800000006</v>
+        <v>-5.704280400000009</v>
       </c>
       <c r="Q55">
-        <v>2.10413219999999</v>
+        <v>1.495719599999987</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1740739984344756</v>
+        <v>0.1768625636178338</v>
       </c>
       <c r="T55">
-        <v>1.240507602420139</v>
+        <v>1.26747515899449</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2104920866790876</v>
+        <v>0.2065940850739193</v>
       </c>
       <c r="W55">
-        <v>0.11589976167551</v>
+        <v>0.1164719883111487</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8419683467163503</v>
+        <v>0.8263763402956771</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1442516529522238</v>
+        <v>0.1452616529522238</v>
       </c>
       <c r="C56">
-        <v>89.51015854198727</v>
+        <v>80.18616917709238</v>
       </c>
       <c r="D56">
-        <v>374.0141585419873</v>
+        <v>370.2161691770925</v>
       </c>
       <c r="E56">
-        <v>278.9040000000001</v>
+        <v>284.4300000000001</v>
       </c>
       <c r="F56">
-        <v>298.4040000000001</v>
+        <v>303.9300000000001</v>
       </c>
       <c r="G56">
         <v>13.9</v>
@@ -5879,37 +5879,37 @@
         <v>36.2</v>
       </c>
       <c r="M56">
-        <v>43.80570720000001</v>
+        <v>44.61692400000001</v>
       </c>
       <c r="N56">
-        <v>-7.605707200000012</v>
+        <v>-8.416924000000009</v>
       </c>
       <c r="O56">
-        <v>-1.901426800000003</v>
+        <v>-2.104231000000002</v>
       </c>
       <c r="P56">
-        <v>-5.704280400000009</v>
+        <v>-6.312693000000007</v>
       </c>
       <c r="Q56">
-        <v>1.495719599999987</v>
+        <v>0.8873069999999892</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1768625636178338</v>
+        <v>0.1797750650315634</v>
       </c>
       <c r="T56">
-        <v>1.26747515899449</v>
+        <v>1.295641273638813</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2065940850739193</v>
+        <v>0.2028378289816662</v>
       </c>
       <c r="W56">
-        <v>0.1164719883111487</v>
+        <v>0.1170234067054914</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8263763402956771</v>
+        <v>0.8113513159266648</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1452616529522238</v>
+        <v>0.1785475249793922</v>
       </c>
       <c r="C57">
-        <v>80.18616917709238</v>
+        <v>-18.1699459721749</v>
       </c>
       <c r="D57">
-        <v>370.2161691770925</v>
+        <v>277.3860540278251</v>
       </c>
       <c r="E57">
-        <v>284.4300000000001</v>
+        <v>289.956</v>
       </c>
       <c r="F57">
-        <v>303.9300000000001</v>
+        <v>309.456</v>
       </c>
       <c r="G57">
         <v>13.9</v>
@@ -5961,45 +5961,45 @@
         <v>36.2</v>
       </c>
       <c r="M57">
-        <v>44.61692400000001</v>
+        <v>62.1387648</v>
       </c>
       <c r="N57">
-        <v>-8.416924000000009</v>
+        <v>-25.9387648</v>
       </c>
       <c r="O57">
-        <v>-2.104231000000002</v>
+        <v>-6.4846912</v>
       </c>
       <c r="P57">
-        <v>-6.312693000000007</v>
+        <v>-19.4540736</v>
       </c>
       <c r="Q57">
-        <v>0.8873069999999892</v>
+        <v>-12.25407360000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1797750650315634</v>
+        <v>0.1874469347531179</v>
       </c>
       <c r="T57">
-        <v>1.295641273638813</v>
+        <v>1.369834117321211</v>
       </c>
       <c r="U57">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.2028378289816662</v>
+        <v>0.1456417749713622</v>
       </c>
       <c r="W57">
-        <v>0.1170234067054914</v>
+        <v>0.1715551315857505</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8113513159266648</v>
+        <v>0.5825670998854486</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1785475249793922</v>
+        <v>0.1800975249793922</v>
       </c>
       <c r="C58">
-        <v>-18.1699459721749</v>
+        <v>-26.89740768049074</v>
       </c>
       <c r="D58">
-        <v>277.3860540278251</v>
+        <v>274.1845923195093</v>
       </c>
       <c r="E58">
-        <v>289.956</v>
+        <v>295.482</v>
       </c>
       <c r="F58">
-        <v>309.456</v>
+        <v>314.982</v>
       </c>
       <c r="G58">
         <v>13.9</v>
@@ -6043,37 +6043,37 @@
         <v>36.2</v>
       </c>
       <c r="M58">
-        <v>62.1387648</v>
+        <v>63.24838560000001</v>
       </c>
       <c r="N58">
-        <v>-25.9387648</v>
+        <v>-27.0483856</v>
       </c>
       <c r="O58">
-        <v>-6.4846912</v>
+        <v>-6.762096400000001</v>
       </c>
       <c r="P58">
-        <v>-19.4540736</v>
+        <v>-20.2862892</v>
       </c>
       <c r="Q58">
-        <v>-12.25407360000001</v>
+        <v>-13.08628920000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1874469347531179</v>
+        <v>0.1907410495148184</v>
       </c>
       <c r="T58">
-        <v>1.369834117321211</v>
+        <v>1.401690724700774</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1456417749713622</v>
+        <v>0.1430866561122155</v>
       </c>
       <c r="W58">
-        <v>0.1715551315857505</v>
+        <v>0.1720681994526671</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5825670998854486</v>
+        <v>0.5723466244488618</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1800975249793922</v>
+        <v>0.1816475249793922</v>
       </c>
       <c r="C59">
-        <v>-26.89740768049074</v>
+        <v>-35.55181298754155</v>
       </c>
       <c r="D59">
-        <v>274.1845923195093</v>
+        <v>271.0561870124585</v>
       </c>
       <c r="E59">
-        <v>295.482</v>
+        <v>301.008</v>
       </c>
       <c r="F59">
-        <v>314.982</v>
+        <v>320.508</v>
       </c>
       <c r="G59">
         <v>13.9</v>
@@ -6125,37 +6125,37 @@
         <v>36.2</v>
       </c>
       <c r="M59">
-        <v>63.24838560000001</v>
+        <v>64.35800640000001</v>
       </c>
       <c r="N59">
-        <v>-27.0483856</v>
+        <v>-28.1580064</v>
       </c>
       <c r="O59">
-        <v>-6.762096400000001</v>
+        <v>-7.039501600000001</v>
       </c>
       <c r="P59">
-        <v>-20.2862892</v>
+        <v>-21.1185048</v>
       </c>
       <c r="Q59">
-        <v>-13.08628920000001</v>
+        <v>-13.91850480000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1907410495148184</v>
+        <v>0.1941920268842188</v>
       </c>
       <c r="T59">
-        <v>1.401690724700774</v>
+        <v>1.435064313384126</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1430866561122155</v>
+        <v>0.1406196447999359</v>
       </c>
       <c r="W59">
-        <v>0.1720681994526671</v>
+        <v>0.1725635753241729</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5723466244488618</v>
+        <v>0.5624785791997435</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1816475249793921</v>
+        <v>0.1831975249793921</v>
       </c>
       <c r="C60">
-        <v>-35.55181298754138</v>
+        <v>-44.13563437065818</v>
       </c>
       <c r="D60">
-        <v>271.0561870124586</v>
+        <v>267.9983656293418</v>
       </c>
       <c r="E60">
-        <v>301.008</v>
+        <v>306.534</v>
       </c>
       <c r="F60">
-        <v>320.508</v>
+        <v>326.034</v>
       </c>
       <c r="G60">
         <v>13.9</v>
@@ -6207,37 +6207,37 @@
         <v>36.2</v>
       </c>
       <c r="M60">
-        <v>64.35800639999999</v>
+        <v>65.4676272</v>
       </c>
       <c r="N60">
-        <v>-28.15800639999999</v>
+        <v>-29.26762719999999</v>
       </c>
       <c r="O60">
-        <v>-7.039501599999998</v>
+        <v>-7.316906799999998</v>
       </c>
       <c r="P60">
-        <v>-21.11850479999999</v>
+        <v>-21.95072039999999</v>
       </c>
       <c r="Q60">
-        <v>-13.9185048</v>
+        <v>-14.7507204</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1941920268842187</v>
+        <v>0.1978113446131021</v>
       </c>
       <c r="T60">
-        <v>1.435064313384125</v>
+        <v>1.47006588200325</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1406196447999359</v>
+        <v>0.1382362609897675</v>
       </c>
       <c r="W60">
-        <v>0.1725635753241729</v>
+        <v>0.1730421587932547</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5624785791997435</v>
+        <v>0.55294504395907</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1831975249793921</v>
+        <v>0.1847475249793921</v>
       </c>
       <c r="C61">
-        <v>-44.13563437065818</v>
+        <v>-52.65123398236119</v>
       </c>
       <c r="D61">
-        <v>267.9983656293418</v>
+        <v>265.0087660176388</v>
       </c>
       <c r="E61">
-        <v>306.534</v>
+        <v>312.06</v>
       </c>
       <c r="F61">
-        <v>326.034</v>
+        <v>331.56</v>
       </c>
       <c r="G61">
         <v>13.9</v>
@@ -6289,37 +6289,37 @@
         <v>36.2</v>
       </c>
       <c r="M61">
-        <v>65.4676272</v>
+        <v>66.577248</v>
       </c>
       <c r="N61">
-        <v>-29.26762719999999</v>
+        <v>-30.37724799999999</v>
       </c>
       <c r="O61">
-        <v>-7.316906799999998</v>
+        <v>-7.594311999999999</v>
       </c>
       <c r="P61">
-        <v>-21.95072039999999</v>
+        <v>-22.782936</v>
       </c>
       <c r="Q61">
-        <v>-14.7507204</v>
+        <v>-15.582936</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1978113446131021</v>
+        <v>0.2016116282284297</v>
       </c>
       <c r="T61">
-        <v>1.47006588200325</v>
+        <v>1.506817529053331</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1382362609897675</v>
+        <v>0.1359323233066047</v>
       </c>
       <c r="W61">
-        <v>0.1730421587932547</v>
+        <v>0.1735047894800338</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.55294504395907</v>
+        <v>0.5437292932264188</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1847475249793921</v>
+        <v>0.1862975249793922</v>
       </c>
       <c r="C62">
-        <v>-52.65123398236119</v>
+        <v>-61.10086973599891</v>
       </c>
       <c r="D62">
-        <v>265.0087660176388</v>
+        <v>262.0851302640011</v>
       </c>
       <c r="E62">
-        <v>312.06</v>
+        <v>317.586</v>
       </c>
       <c r="F62">
-        <v>331.56</v>
+        <v>337.086</v>
       </c>
       <c r="G62">
         <v>13.9</v>
@@ -6371,37 +6371,37 @@
         <v>36.2</v>
       </c>
       <c r="M62">
-        <v>66.577248</v>
+        <v>67.6868688</v>
       </c>
       <c r="N62">
-        <v>-30.37724799999999</v>
+        <v>-31.4868688</v>
       </c>
       <c r="O62">
-        <v>-7.594311999999999</v>
+        <v>-7.871717199999999</v>
       </c>
       <c r="P62">
-        <v>-22.782936</v>
+        <v>-23.6151516</v>
       </c>
       <c r="Q62">
-        <v>-15.582936</v>
+        <v>-16.4151516</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2016116282284297</v>
+        <v>0.2056067981830048</v>
       </c>
       <c r="T62">
-        <v>1.506817529053331</v>
+        <v>1.545453875952135</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1359323233066047</v>
+        <v>0.1337039245638735</v>
       </c>
       <c r="W62">
-        <v>0.1735047894800338</v>
+        <v>0.1739522519475742</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5437292932264188</v>
+        <v>0.5348156982554939</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1862975249793922</v>
+        <v>0.1878475249793921</v>
       </c>
       <c r="C63">
-        <v>-61.10086973599891</v>
+        <v>-69.48670099295413</v>
       </c>
       <c r="D63">
-        <v>262.0851302640011</v>
+        <v>259.2252990070459</v>
       </c>
       <c r="E63">
-        <v>317.586</v>
+        <v>323.112</v>
       </c>
       <c r="F63">
-        <v>337.086</v>
+        <v>342.612</v>
       </c>
       <c r="G63">
         <v>13.9</v>
@@ -6453,37 +6453,37 @@
         <v>36.2</v>
       </c>
       <c r="M63">
-        <v>67.6868688</v>
+        <v>68.7964896</v>
       </c>
       <c r="N63">
-        <v>-31.4868688</v>
+        <v>-32.5964896</v>
       </c>
       <c r="O63">
-        <v>-7.871717199999999</v>
+        <v>-8.1491224</v>
       </c>
       <c r="P63">
-        <v>-23.6151516</v>
+        <v>-24.4473672</v>
       </c>
       <c r="Q63">
-        <v>-16.4151516</v>
+        <v>-17.2473672</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2056067981830048</v>
+        <v>0.2098122402404523</v>
       </c>
       <c r="T63">
-        <v>1.545453875952135</v>
+        <v>1.586123714792981</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1337039245638735</v>
+        <v>0.1315474096515529</v>
       </c>
       <c r="W63">
-        <v>0.1739522519475742</v>
+        <v>0.1743852801419682</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5348156982554939</v>
+        <v>0.5261896386062117</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1878475249793921</v>
+        <v>0.1893975249793922</v>
       </c>
       <c r="C64">
-        <v>-69.48670099295413</v>
+        <v>-77.81079388152295</v>
       </c>
       <c r="D64">
-        <v>259.2252990070459</v>
+        <v>256.4272061184771</v>
       </c>
       <c r="E64">
-        <v>323.112</v>
+        <v>328.638</v>
       </c>
       <c r="F64">
-        <v>342.612</v>
+        <v>348.138</v>
       </c>
       <c r="G64">
         <v>13.9</v>
@@ -6535,37 +6535,37 @@
         <v>36.2</v>
       </c>
       <c r="M64">
-        <v>68.7964896</v>
+        <v>69.9061104</v>
       </c>
       <c r="N64">
-        <v>-32.5964896</v>
+        <v>-33.7061104</v>
       </c>
       <c r="O64">
-        <v>-8.1491224</v>
+        <v>-8.4265276</v>
       </c>
       <c r="P64">
-        <v>-24.4473672</v>
+        <v>-25.2795828</v>
       </c>
       <c r="Q64">
-        <v>-17.2473672</v>
+        <v>-18.0795828</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2098122402404523</v>
+        <v>0.2142450034901943</v>
       </c>
       <c r="T64">
-        <v>1.586123714792981</v>
+        <v>1.628991923300899</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1315474096515529</v>
+        <v>0.1294593555300997</v>
       </c>
       <c r="W64">
-        <v>0.1743852801419682</v>
+        <v>0.174804561409556</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5261896386062117</v>
+        <v>0.5178374221203987</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1893975249793922</v>
+        <v>0.1909475249793922</v>
       </c>
       <c r="C65">
-        <v>-77.81079388152295</v>
+        <v>-86.07512627499693</v>
       </c>
       <c r="D65">
-        <v>256.4272061184771</v>
+        <v>253.6888737250031</v>
       </c>
       <c r="E65">
-        <v>328.638</v>
+        <v>334.164</v>
       </c>
       <c r="F65">
-        <v>348.138</v>
+        <v>353.664</v>
       </c>
       <c r="G65">
         <v>13.9</v>
@@ -6617,37 +6617,37 @@
         <v>36.2</v>
       </c>
       <c r="M65">
-        <v>69.9061104</v>
+        <v>71.0157312</v>
       </c>
       <c r="N65">
-        <v>-33.7061104</v>
+        <v>-34.8157312</v>
       </c>
       <c r="O65">
-        <v>-8.4265276</v>
+        <v>-8.7039328</v>
       </c>
       <c r="P65">
-        <v>-25.2795828</v>
+        <v>-26.1117984</v>
       </c>
       <c r="Q65">
-        <v>-18.0795828</v>
+        <v>-18.91179840000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2142450034901943</v>
+        <v>0.2189240313649219</v>
       </c>
       <c r="T65">
-        <v>1.628991923300899</v>
+        <v>1.674241698948146</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1294593555300997</v>
+        <v>0.1274365530999419</v>
       </c>
       <c r="W65">
-        <v>0.174804561409556</v>
+        <v>0.1752107401375317</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5178374221203987</v>
+        <v>0.5097462123997676</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1909475249793922</v>
+        <v>0.1924975249793922</v>
       </c>
       <c r="C66">
-        <v>-86.07512627499693</v>
+        <v>-94.28159245415708</v>
       </c>
       <c r="D66">
-        <v>253.6888737250031</v>
+        <v>251.008407545843</v>
       </c>
       <c r="E66">
-        <v>334.164</v>
+        <v>339.6900000000001</v>
       </c>
       <c r="F66">
-        <v>353.664</v>
+        <v>359.1900000000001</v>
       </c>
       <c r="G66">
         <v>13.9</v>
@@ -6699,37 +6699,37 @@
         <v>36.2</v>
       </c>
       <c r="M66">
-        <v>71.0157312</v>
+        <v>72.12535200000001</v>
       </c>
       <c r="N66">
-        <v>-34.8157312</v>
+        <v>-35.925352</v>
       </c>
       <c r="O66">
-        <v>-8.7039328</v>
+        <v>-8.981338000000001</v>
       </c>
       <c r="P66">
-        <v>-26.1117984</v>
+        <v>-26.944014</v>
       </c>
       <c r="Q66">
-        <v>-18.91179840000001</v>
+        <v>-19.74401400000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2189240313649219</v>
+        <v>0.2238704322610625</v>
       </c>
       <c r="T66">
-        <v>1.674241698948146</v>
+        <v>1.722077176060951</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1274365530999419</v>
+        <v>0.1254759907445582</v>
       </c>
       <c r="W66">
-        <v>0.1752107401375317</v>
+        <v>0.1756044210584927</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5097462123997676</v>
+        <v>0.5019039629782327</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1924975249793922</v>
+        <v>0.2179690239329616</v>
       </c>
       <c r="C67">
-        <v>-94.28159245415708</v>
+        <v>-136.9429623603637</v>
       </c>
       <c r="D67">
-        <v>251.008407545843</v>
+        <v>213.8730376396364</v>
       </c>
       <c r="E67">
-        <v>339.6900000000001</v>
+        <v>345.216</v>
       </c>
       <c r="F67">
-        <v>359.1900000000001</v>
+        <v>364.716</v>
       </c>
       <c r="G67">
         <v>13.9</v>
@@ -6781,45 +6781,45 @@
         <v>36.2</v>
       </c>
       <c r="M67">
-        <v>72.12535200000001</v>
+        <v>86.0000328</v>
       </c>
       <c r="N67">
-        <v>-35.925352</v>
+        <v>-49.8000328</v>
       </c>
       <c r="O67">
-        <v>-8.981338000000001</v>
+        <v>-12.4500082</v>
       </c>
       <c r="P67">
-        <v>-26.944014</v>
+        <v>-37.3500246</v>
       </c>
       <c r="Q67">
-        <v>-19.74401400000001</v>
+        <v>-30.1500246</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2238704322610625</v>
+        <v>0.2315239713086511</v>
       </c>
       <c r="T67">
-        <v>1.722077176060951</v>
+        <v>1.796092748116287</v>
       </c>
       <c r="U67">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1254759907445582</v>
+        <v>0.105232518004342</v>
       </c>
       <c r="W67">
-        <v>0.1756044210584927</v>
+        <v>0.2109861722545762</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.5019039629782327</v>
+        <v>0.4209300720173679</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2179690239329616</v>
+        <v>0.2198690239329616</v>
       </c>
       <c r="C68">
-        <v>-136.9429623603637</v>
+        <v>-144.8034315400829</v>
       </c>
       <c r="D68">
-        <v>213.8730376396364</v>
+        <v>211.5385684599171</v>
       </c>
       <c r="E68">
-        <v>345.216</v>
+        <v>350.742</v>
       </c>
       <c r="F68">
-        <v>364.716</v>
+        <v>370.242</v>
       </c>
       <c r="G68">
         <v>13.9</v>
@@ -6863,37 +6863,37 @@
         <v>36.2</v>
       </c>
       <c r="M68">
-        <v>86.0000328</v>
+        <v>87.3030636</v>
       </c>
       <c r="N68">
-        <v>-49.8000328</v>
+        <v>-51.1030636</v>
       </c>
       <c r="O68">
-        <v>-12.4500082</v>
+        <v>-12.7757659</v>
       </c>
       <c r="P68">
-        <v>-37.3500246</v>
+        <v>-38.3272977</v>
       </c>
       <c r="Q68">
-        <v>-30.1500246</v>
+        <v>-31.12729770000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2315239713086511</v>
+        <v>0.2371519704392163</v>
       </c>
       <c r="T68">
-        <v>1.796092748116287</v>
+        <v>1.850519801089508</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.105232518004342</v>
+        <v>0.1036618834072622</v>
       </c>
       <c r="W68">
-        <v>0.2109861722545762</v>
+        <v>0.2113565278925676</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4209300720173679</v>
+        <v>0.4146475336290489</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2198690239329616</v>
+        <v>0.2217690239329617</v>
       </c>
       <c r="C69">
-        <v>-144.8034315400829</v>
+        <v>-152.6134885354037</v>
       </c>
       <c r="D69">
-        <v>211.5385684599171</v>
+        <v>209.2545114645963</v>
       </c>
       <c r="E69">
-        <v>350.742</v>
+        <v>356.268</v>
       </c>
       <c r="F69">
-        <v>370.242</v>
+        <v>375.768</v>
       </c>
       <c r="G69">
         <v>13.9</v>
@@ -6945,37 +6945,37 @@
         <v>36.2</v>
       </c>
       <c r="M69">
-        <v>87.3030636</v>
+        <v>88.6060944</v>
       </c>
       <c r="N69">
-        <v>-51.1030636</v>
+        <v>-52.4060944</v>
       </c>
       <c r="O69">
-        <v>-12.7757659</v>
+        <v>-13.1015236</v>
       </c>
       <c r="P69">
-        <v>-38.3272977</v>
+        <v>-39.3045708</v>
       </c>
       <c r="Q69">
-        <v>-31.12729770000001</v>
+        <v>-32.1045708</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2371519704392163</v>
+        <v>0.2431317195154418</v>
       </c>
       <c r="T69">
-        <v>1.850519801089508</v>
+        <v>1.908348544873555</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1036618834072622</v>
+        <v>0.1021374439453907</v>
       </c>
       <c r="W69">
-        <v>0.2113565278925676</v>
+        <v>0.2117159907176769</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4146475336290489</v>
+        <v>0.4085497757815629</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2217690239329617</v>
+        <v>0.2236690239329617</v>
       </c>
       <c r="C70">
-        <v>-152.6134885354037</v>
+        <v>-160.3747488578114</v>
       </c>
       <c r="D70">
-        <v>209.2545114645963</v>
+        <v>207.0192511421886</v>
       </c>
       <c r="E70">
-        <v>356.268</v>
+        <v>361.794</v>
       </c>
       <c r="F70">
-        <v>375.768</v>
+        <v>381.294</v>
       </c>
       <c r="G70">
         <v>13.9</v>
@@ -7027,37 +7027,37 @@
         <v>36.2</v>
       </c>
       <c r="M70">
-        <v>88.6060944</v>
+        <v>89.90912520000002</v>
       </c>
       <c r="N70">
-        <v>-52.4060944</v>
+        <v>-53.70912520000002</v>
       </c>
       <c r="O70">
-        <v>-13.1015236</v>
+        <v>-13.4272813</v>
       </c>
       <c r="P70">
-        <v>-39.3045708</v>
+        <v>-40.28184390000001</v>
       </c>
       <c r="Q70">
-        <v>-32.1045708</v>
+        <v>-33.08184390000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2431317195154418</v>
+        <v>0.2494972588546496</v>
       </c>
       <c r="T70">
-        <v>1.908348544873555</v>
+        <v>1.969908175353347</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1021374439453907</v>
+        <v>0.100657191134588</v>
       </c>
       <c r="W70">
-        <v>0.2117159907176769</v>
+        <v>0.2120650343304642</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4085497757815629</v>
+        <v>0.4026287645383518</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2236690239329617</v>
+        <v>0.2255690239329617</v>
       </c>
       <c r="C71">
-        <v>-160.3747488578114</v>
+        <v>-168.0887597206664</v>
       </c>
       <c r="D71">
-        <v>207.0192511421886</v>
+        <v>204.8312402793337</v>
       </c>
       <c r="E71">
-        <v>361.794</v>
+        <v>367.3200000000001</v>
       </c>
       <c r="F71">
-        <v>381.294</v>
+        <v>386.8200000000001</v>
       </c>
       <c r="G71">
         <v>13.9</v>
@@ -7109,37 +7109,37 @@
         <v>36.2</v>
       </c>
       <c r="M71">
-        <v>89.90912520000002</v>
+        <v>91.21215600000002</v>
       </c>
       <c r="N71">
-        <v>-53.70912520000002</v>
+        <v>-55.01215600000002</v>
       </c>
       <c r="O71">
-        <v>-13.4272813</v>
+        <v>-13.753039</v>
       </c>
       <c r="P71">
-        <v>-40.28184390000001</v>
+        <v>-41.25911700000002</v>
       </c>
       <c r="Q71">
-        <v>-33.08184390000002</v>
+        <v>-34.05911700000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2494972588546496</v>
+        <v>0.2562871674831379</v>
       </c>
       <c r="T71">
-        <v>1.969908175353347</v>
+        <v>2.035571781198458</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.100657191134588</v>
+        <v>0.0992192312612367</v>
       </c>
       <c r="W71">
-        <v>0.2120650343304642</v>
+        <v>0.2124041052686004</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4026287645383518</v>
+        <v>0.3968769250449468</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2255690239329617</v>
+        <v>0.2274690239329616</v>
       </c>
       <c r="C72">
-        <v>-168.0887597206664</v>
+        <v>-175.7570036107109</v>
       </c>
       <c r="D72">
-        <v>204.8312402793337</v>
+        <v>202.6889963892892</v>
       </c>
       <c r="E72">
-        <v>367.3200000000001</v>
+        <v>372.8460000000001</v>
       </c>
       <c r="F72">
-        <v>386.8200000000001</v>
+        <v>392.3460000000001</v>
       </c>
       <c r="G72">
         <v>13.9</v>
@@ -7191,37 +7191,37 @@
         <v>36.2</v>
       </c>
       <c r="M72">
-        <v>91.21215600000002</v>
+        <v>92.51518680000002</v>
       </c>
       <c r="N72">
-        <v>-55.01215600000002</v>
+        <v>-56.31518680000002</v>
       </c>
       <c r="O72">
-        <v>-13.753039</v>
+        <v>-14.07879670000001</v>
       </c>
       <c r="P72">
-        <v>-41.25911700000002</v>
+        <v>-42.23639010000002</v>
       </c>
       <c r="Q72">
-        <v>-34.05911700000002</v>
+        <v>-35.03639010000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2562871674831379</v>
+        <v>0.2635453456722117</v>
       </c>
       <c r="T72">
-        <v>2.035571781198458</v>
+        <v>2.105763911584613</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0992192312612367</v>
+        <v>0.09782177729981083</v>
       </c>
       <c r="W72">
-        <v>0.2124041052686004</v>
+        <v>0.2127336249127046</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3968769250449468</v>
+        <v>0.3912871091992434</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2274690239329616</v>
+        <v>0.2293690239329617</v>
       </c>
       <c r="C73">
-        <v>-175.7570036107108</v>
+        <v>-183.3809016377782</v>
       </c>
       <c r="D73">
-        <v>202.6889963892892</v>
+        <v>200.5910983622218</v>
       </c>
       <c r="E73">
-        <v>372.846</v>
+        <v>378.372</v>
       </c>
       <c r="F73">
-        <v>392.346</v>
+        <v>397.872</v>
       </c>
       <c r="G73">
         <v>13.9</v>
@@ -7273,37 +7273,37 @@
         <v>36.2</v>
       </c>
       <c r="M73">
-        <v>92.51518680000001</v>
+        <v>93.81821760000001</v>
       </c>
       <c r="N73">
-        <v>-56.31518680000001</v>
+        <v>-57.61821760000001</v>
       </c>
       <c r="O73">
-        <v>-14.0787967</v>
+        <v>-14.4045544</v>
       </c>
       <c r="P73">
-        <v>-42.23639010000001</v>
+        <v>-43.21366320000001</v>
       </c>
       <c r="Q73">
-        <v>-35.03639010000001</v>
+        <v>-36.01366320000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2635453456722116</v>
+        <v>0.2713219651605049</v>
       </c>
       <c r="T73">
-        <v>2.105763911584612</v>
+        <v>2.180969765569777</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09782177729981084</v>
+        <v>0.09646314150398014</v>
       </c>
       <c r="W73">
-        <v>0.2127336249127046</v>
+        <v>0.2130539912333615</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3912871091992434</v>
+        <v>0.3858525660159206</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2293690239329617</v>
+        <v>0.2312690239329616</v>
       </c>
       <c r="C74">
-        <v>-183.3809016377782</v>
+        <v>-190.9618166786099</v>
       </c>
       <c r="D74">
-        <v>200.5910983622218</v>
+        <v>198.5361833213901</v>
       </c>
       <c r="E74">
-        <v>378.372</v>
+        <v>383.898</v>
       </c>
       <c r="F74">
-        <v>397.872</v>
+        <v>403.398</v>
       </c>
       <c r="G74">
         <v>13.9</v>
@@ -7355,37 +7355,37 @@
         <v>36.2</v>
       </c>
       <c r="M74">
-        <v>93.81821760000001</v>
+        <v>95.12124840000001</v>
       </c>
       <c r="N74">
-        <v>-57.61821760000001</v>
+        <v>-58.92124840000001</v>
       </c>
       <c r="O74">
-        <v>-14.4045544</v>
+        <v>-14.7303121</v>
       </c>
       <c r="P74">
-        <v>-43.21366320000001</v>
+        <v>-44.1909363</v>
       </c>
       <c r="Q74">
-        <v>-36.01366320000001</v>
+        <v>-36.99093630000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2713219651605049</v>
+        <v>0.2796746305368198</v>
       </c>
       <c r="T74">
-        <v>2.180969765569777</v>
+        <v>2.261746423553842</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09646314150398014</v>
+        <v>0.09514172860666534</v>
       </c>
       <c r="W74">
-        <v>0.2130539912333615</v>
+        <v>0.2133655803945483</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3858525660159206</v>
+        <v>0.3805669144266614</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2312690239329616</v>
+        <v>0.2331690239329616</v>
       </c>
       <c r="C75">
-        <v>-190.9618166786099</v>
+        <v>-198.5010563293945</v>
       </c>
       <c r="D75">
-        <v>198.5361833213901</v>
+        <v>196.5229436706055</v>
       </c>
       <c r="E75">
-        <v>383.898</v>
+        <v>389.424</v>
       </c>
       <c r="F75">
-        <v>403.398</v>
+        <v>408.924</v>
       </c>
       <c r="G75">
         <v>13.9</v>
@@ -7437,37 +7437,37 @@
         <v>36.2</v>
       </c>
       <c r="M75">
-        <v>95.12124840000001</v>
+        <v>96.42427920000002</v>
       </c>
       <c r="N75">
-        <v>-58.92124840000001</v>
+        <v>-60.22427920000001</v>
       </c>
       <c r="O75">
-        <v>-14.7303121</v>
+        <v>-15.0560698</v>
       </c>
       <c r="P75">
-        <v>-44.1909363</v>
+        <v>-45.16820940000001</v>
       </c>
       <c r="Q75">
-        <v>-36.99093630000001</v>
+        <v>-37.96820940000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2796746305368198</v>
+        <v>0.2886698086343898</v>
       </c>
       <c r="T75">
-        <v>2.261746423553842</v>
+        <v>2.348736670613606</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09514172860666534</v>
+        <v>0.09385602957144012</v>
       </c>
       <c r="W75">
-        <v>0.2133655803945483</v>
+        <v>0.2136687482270544</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3805669144266614</v>
+        <v>0.3754241182857605</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2331690239329616</v>
+        <v>0.2350690239329616</v>
       </c>
       <c r="C76">
-        <v>-198.5010563293945</v>
+        <v>-205.9998756804702</v>
       </c>
       <c r="D76">
-        <v>196.5229436706055</v>
+        <v>194.5501243195299</v>
       </c>
       <c r="E76">
-        <v>389.424</v>
+        <v>394.95</v>
       </c>
       <c r="F76">
-        <v>408.924</v>
+        <v>414.45</v>
       </c>
       <c r="G76">
         <v>13.9</v>
@@ -7519,37 +7519,37 @@
         <v>36.2</v>
       </c>
       <c r="M76">
-        <v>96.42427920000002</v>
+        <v>97.72731000000002</v>
       </c>
       <c r="N76">
-        <v>-60.22427920000001</v>
+        <v>-61.52731000000001</v>
       </c>
       <c r="O76">
-        <v>-15.0560698</v>
+        <v>-15.3818275</v>
       </c>
       <c r="P76">
-        <v>-45.16820940000001</v>
+        <v>-46.14548250000001</v>
       </c>
       <c r="Q76">
-        <v>-37.96820940000001</v>
+        <v>-38.94548250000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2886698086343898</v>
+        <v>0.2983846009797655</v>
       </c>
       <c r="T76">
-        <v>2.348736670613606</v>
+        <v>2.44268613743815</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09385602957144012</v>
+        <v>0.09260461584382093</v>
       </c>
       <c r="W76">
-        <v>0.2136687482270544</v>
+        <v>0.213963831584027</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3754241182857605</v>
+        <v>0.3704184633752837</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2350690239329616</v>
+        <v>0.2369690239329617</v>
       </c>
       <c r="C77">
-        <v>-205.9998756804702</v>
+        <v>-213.4594799255634</v>
       </c>
       <c r="D77">
-        <v>194.5501243195299</v>
+        <v>192.6165200744366</v>
       </c>
       <c r="E77">
-        <v>394.95</v>
+        <v>400.476</v>
       </c>
       <c r="F77">
-        <v>414.45</v>
+        <v>419.976</v>
       </c>
       <c r="G77">
         <v>13.9</v>
@@ -7601,37 +7601,37 @@
         <v>36.2</v>
       </c>
       <c r="M77">
-        <v>97.72731000000002</v>
+        <v>99.0303408</v>
       </c>
       <c r="N77">
-        <v>-61.52731000000001</v>
+        <v>-62.8303408</v>
       </c>
       <c r="O77">
-        <v>-15.3818275</v>
+        <v>-15.7075852</v>
       </c>
       <c r="P77">
-        <v>-46.14548250000001</v>
+        <v>-47.1227556</v>
       </c>
       <c r="Q77">
-        <v>-38.94548250000002</v>
+        <v>-39.92275560000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2983846009797655</v>
+        <v>0.3089089593539224</v>
       </c>
       <c r="T77">
-        <v>2.44268613743815</v>
+        <v>2.544464726498073</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09260461584382093</v>
+        <v>0.09138613405640224</v>
       </c>
       <c r="W77">
-        <v>0.213963831584027</v>
+        <v>0.2142511495895003</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3704184633752837</v>
+        <v>0.365544536225609</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2369690239329617</v>
+        <v>0.2388690239329616</v>
       </c>
       <c r="C78">
-        <v>-213.4594799255634</v>
+        <v>-220.8810268169617</v>
       </c>
       <c r="D78">
-        <v>192.6165200744366</v>
+        <v>190.7209731830383</v>
       </c>
       <c r="E78">
-        <v>400.476</v>
+        <v>406.002</v>
       </c>
       <c r="F78">
-        <v>419.976</v>
+        <v>425.502</v>
       </c>
       <c r="G78">
         <v>13.9</v>
@@ -7683,37 +7683,37 @@
         <v>36.2</v>
       </c>
       <c r="M78">
-        <v>99.0303408</v>
+        <v>100.3333716</v>
       </c>
       <c r="N78">
-        <v>-62.8303408</v>
+        <v>-64.1333716</v>
       </c>
       <c r="O78">
-        <v>-15.7075852</v>
+        <v>-16.0333429</v>
       </c>
       <c r="P78">
-        <v>-47.1227556</v>
+        <v>-48.1000287</v>
       </c>
       <c r="Q78">
-        <v>-39.92275560000001</v>
+        <v>-40.90002870000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3089089593539224</v>
+        <v>0.320348479325832</v>
       </c>
       <c r="T78">
-        <v>2.544464726498073</v>
+        <v>2.655093627650163</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09138613405640224</v>
+        <v>0.09019930114657883</v>
       </c>
       <c r="W78">
-        <v>0.2142511495895003</v>
+        <v>0.2145310047896367</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.365544536225609</v>
+        <v>0.3607972045863154</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2388690239329616</v>
+        <v>0.2407690239329616</v>
       </c>
       <c r="C79">
-        <v>-220.8810268169617</v>
+        <v>-228.2656289771304</v>
       </c>
       <c r="D79">
-        <v>190.7209731830383</v>
+        <v>188.8623710228696</v>
       </c>
       <c r="E79">
-        <v>406.002</v>
+        <v>411.528</v>
       </c>
       <c r="F79">
-        <v>425.502</v>
+        <v>431.028</v>
       </c>
       <c r="G79">
         <v>13.9</v>
@@ -7765,37 +7765,37 @@
         <v>36.2</v>
       </c>
       <c r="M79">
-        <v>100.3333716</v>
+        <v>101.6364024</v>
       </c>
       <c r="N79">
-        <v>-64.1333716</v>
+        <v>-65.43640240000001</v>
       </c>
       <c r="O79">
-        <v>-16.0333429</v>
+        <v>-16.3591006</v>
       </c>
       <c r="P79">
-        <v>-48.1000287</v>
+        <v>-49.0773018</v>
       </c>
       <c r="Q79">
-        <v>-40.90002870000001</v>
+        <v>-41.87730180000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.320348479325832</v>
+        <v>0.3328279556588244</v>
       </c>
       <c r="T79">
-        <v>2.655093627650163</v>
+        <v>2.775779701634261</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09019930114657883</v>
+        <v>0.08904289984982781</v>
       </c>
       <c r="W79">
-        <v>0.2145310047896367</v>
+        <v>0.2148036842154106</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3607972045863154</v>
+        <v>0.3561715993993113</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2407690239329616</v>
+        <v>0.2426690239329617</v>
       </c>
       <c r="C80">
-        <v>-228.2656289771304</v>
+        <v>-235.6143560764716</v>
       </c>
       <c r="D80">
-        <v>188.8623710228696</v>
+        <v>187.0396439235285</v>
       </c>
       <c r="E80">
-        <v>411.528</v>
+        <v>417.054</v>
       </c>
       <c r="F80">
-        <v>431.028</v>
+        <v>436.554</v>
       </c>
       <c r="G80">
         <v>13.9</v>
@@ -7847,37 +7847,37 @@
         <v>36.2</v>
       </c>
       <c r="M80">
-        <v>101.6364024</v>
+        <v>102.9394332</v>
       </c>
       <c r="N80">
-        <v>-65.43640240000001</v>
+        <v>-66.73943320000001</v>
       </c>
       <c r="O80">
-        <v>-16.3591006</v>
+        <v>-16.6848583</v>
       </c>
       <c r="P80">
-        <v>-49.0773018</v>
+        <v>-50.05457490000001</v>
       </c>
       <c r="Q80">
-        <v>-41.87730180000001</v>
+        <v>-42.85457490000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3328279556588244</v>
+        <v>0.3464959535473399</v>
       </c>
       <c r="T80">
-        <v>2.775779701634261</v>
+        <v>2.90795968742637</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08904289984982781</v>
+        <v>0.08791577453527304</v>
       </c>
       <c r="W80">
-        <v>0.2148036842154106</v>
+        <v>0.2150694603645826</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3561715993993113</v>
+        <v>0.3516630981410922</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2426690239329617</v>
+        <v>0.2445690239329616</v>
       </c>
       <c r="C81">
-        <v>-235.6143560764716</v>
+        <v>-242.9282368861824</v>
       </c>
       <c r="D81">
-        <v>187.0396439235285</v>
+        <v>185.2517631138176</v>
       </c>
       <c r="E81">
-        <v>417.054</v>
+        <v>422.58</v>
       </c>
       <c r="F81">
-        <v>436.554</v>
+        <v>442.08</v>
       </c>
       <c r="G81">
         <v>13.9</v>
@@ -7929,37 +7929,37 @@
         <v>36.2</v>
       </c>
       <c r="M81">
-        <v>102.9394332</v>
+        <v>104.242464</v>
       </c>
       <c r="N81">
-        <v>-66.73943320000001</v>
+        <v>-68.04246400000001</v>
       </c>
       <c r="O81">
-        <v>-16.6848583</v>
+        <v>-17.010616</v>
       </c>
       <c r="P81">
-        <v>-50.05457490000001</v>
+        <v>-51.03184800000001</v>
       </c>
       <c r="Q81">
-        <v>-42.85457490000001</v>
+        <v>-43.83184800000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3464959535473399</v>
+        <v>0.3615307512247069</v>
       </c>
       <c r="T81">
-        <v>2.90795968742637</v>
+        <v>3.053357671797688</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08791577453527304</v>
+        <v>0.08681682735358212</v>
       </c>
       <c r="W81">
-        <v>0.2150694603645826</v>
+        <v>0.2153285921100254</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3516630981410922</v>
+        <v>0.3472673094143285</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2445690239329616</v>
+        <v>0.2464690239329617</v>
       </c>
       <c r="C82">
-        <v>-242.9282368861824</v>
+        <v>-250.2082612144906</v>
       </c>
       <c r="D82">
-        <v>185.2517631138176</v>
+        <v>183.4977387855095</v>
       </c>
       <c r="E82">
-        <v>422.58</v>
+        <v>428.1060000000001</v>
       </c>
       <c r="F82">
-        <v>442.08</v>
+        <v>447.6060000000001</v>
       </c>
       <c r="G82">
         <v>13.9</v>
@@ -8011,37 +8011,37 @@
         <v>36.2</v>
       </c>
       <c r="M82">
-        <v>104.242464</v>
+        <v>105.5454948</v>
       </c>
       <c r="N82">
-        <v>-68.04246400000001</v>
+        <v>-69.34549480000001</v>
       </c>
       <c r="O82">
-        <v>-17.010616</v>
+        <v>-17.3363737</v>
       </c>
       <c r="P82">
-        <v>-51.03184800000001</v>
+        <v>-52.00912110000001</v>
       </c>
       <c r="Q82">
-        <v>-43.83184800000002</v>
+        <v>-44.80912110000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3615307512247069</v>
+        <v>0.378148159183902</v>
       </c>
       <c r="T82">
-        <v>3.053357671797688</v>
+        <v>3.214060707155461</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08681682735358212</v>
+        <v>0.08574501467020457</v>
       </c>
       <c r="W82">
-        <v>0.2153285921100254</v>
+        <v>0.2155813255407658</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3472673094143285</v>
+        <v>0.3429800586808183</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2464690239329617</v>
+        <v>0.2483690239329616</v>
       </c>
       <c r="C83">
-        <v>-250.2082612144906</v>
+        <v>-257.4553817339232</v>
       </c>
       <c r="D83">
-        <v>183.4977387855095</v>
+        <v>181.7766182660769</v>
       </c>
       <c r="E83">
-        <v>428.1060000000001</v>
+        <v>433.6320000000001</v>
       </c>
       <c r="F83">
-        <v>447.6060000000001</v>
+        <v>453.1320000000001</v>
       </c>
       <c r="G83">
         <v>13.9</v>
@@ -8093,37 +8093,37 @@
         <v>36.2</v>
       </c>
       <c r="M83">
-        <v>105.5454948</v>
+        <v>106.8485256</v>
       </c>
       <c r="N83">
-        <v>-69.34549480000001</v>
+        <v>-70.64852560000001</v>
       </c>
       <c r="O83">
-        <v>-17.3363737</v>
+        <v>-17.6621314</v>
       </c>
       <c r="P83">
-        <v>-52.00912110000001</v>
+        <v>-52.98639420000001</v>
       </c>
       <c r="Q83">
-        <v>-44.80912110000001</v>
+        <v>-45.78639420000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.378148159183902</v>
+        <v>0.3966119458052299</v>
       </c>
       <c r="T83">
-        <v>3.214060707155461</v>
+        <v>3.392619635330764</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08574501467020457</v>
+        <v>0.08469934375959232</v>
       </c>
       <c r="W83">
-        <v>0.2155813255407658</v>
+        <v>0.2158278947414881</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3429800586808183</v>
+        <v>0.3387973750383693</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2483690239329616</v>
+        <v>0.2502690239329616</v>
       </c>
       <c r="C84">
-        <v>-257.4553817339232</v>
+        <v>-264.6705157066993</v>
       </c>
       <c r="D84">
-        <v>181.7766182660769</v>
+        <v>180.0874842933007</v>
       </c>
       <c r="E84">
-        <v>433.6320000000001</v>
+        <v>439.1580000000001</v>
       </c>
       <c r="F84">
-        <v>453.1320000000001</v>
+        <v>458.6580000000001</v>
       </c>
       <c r="G84">
         <v>13.9</v>
@@ -8175,37 +8175,37 @@
         <v>36.2</v>
       </c>
       <c r="M84">
-        <v>106.8485256</v>
+        <v>108.1515564</v>
       </c>
       <c r="N84">
-        <v>-70.64852560000001</v>
+        <v>-71.95155640000002</v>
       </c>
       <c r="O84">
-        <v>-17.6621314</v>
+        <v>-17.9878891</v>
       </c>
       <c r="P84">
-        <v>-52.98639420000001</v>
+        <v>-53.96366730000001</v>
       </c>
       <c r="Q84">
-        <v>-45.78639420000001</v>
+        <v>-46.76366730000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3966119458052299</v>
+        <v>0.4172479426173022</v>
       </c>
       <c r="T84">
-        <v>3.392619635330764</v>
+        <v>3.592185496232574</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08469934375959232</v>
+        <v>0.08367886973839241</v>
       </c>
       <c r="W84">
-        <v>0.2158278947414881</v>
+        <v>0.2160685225156871</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3387973750383693</v>
+        <v>0.3347154789535696</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2502690239329616</v>
+        <v>0.2521690239329616</v>
       </c>
       <c r="C85">
-        <v>-264.6705157066993</v>
+        <v>-271.8545466148091</v>
       </c>
       <c r="D85">
-        <v>180.0874842933007</v>
+        <v>178.429453385191</v>
       </c>
       <c r="E85">
-        <v>439.1580000000001</v>
+        <v>444.6840000000001</v>
       </c>
       <c r="F85">
-        <v>458.6580000000001</v>
+        <v>464.1840000000001</v>
       </c>
       <c r="G85">
         <v>13.9</v>
@@ -8257,37 +8257,37 @@
         <v>36.2</v>
       </c>
       <c r="M85">
-        <v>108.1515564</v>
+        <v>109.4545872</v>
       </c>
       <c r="N85">
-        <v>-71.95155640000002</v>
+        <v>-73.25458720000002</v>
       </c>
       <c r="O85">
-        <v>-17.9878891</v>
+        <v>-18.3136468</v>
       </c>
       <c r="P85">
-        <v>-53.96366730000001</v>
+        <v>-54.94094040000002</v>
       </c>
       <c r="Q85">
-        <v>-46.76366730000002</v>
+        <v>-47.74094040000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4172479426173022</v>
+        <v>0.4404634390308838</v>
       </c>
       <c r="T85">
-        <v>3.592185496232574</v>
+        <v>3.816697089747111</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08367886973839241</v>
+        <v>0.08268269271769725</v>
       </c>
       <c r="W85">
-        <v>0.2160685225156871</v>
+        <v>0.216303421057167</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3347154789535696</v>
+        <v>0.3307307708707891</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2521690239329616</v>
+        <v>0.2540690239329616</v>
       </c>
       <c r="C86">
-        <v>-271.854546614809</v>
+        <v>-279.0083257008673</v>
       </c>
       <c r="D86">
-        <v>178.429453385191</v>
+        <v>176.8016742991327</v>
       </c>
       <c r="E86">
-        <v>444.684</v>
+        <v>450.21</v>
       </c>
       <c r="F86">
-        <v>464.184</v>
+        <v>469.71</v>
       </c>
       <c r="G86">
         <v>13.9</v>
@@ -8339,37 +8339,37 @@
         <v>36.2</v>
       </c>
       <c r="M86">
-        <v>109.4545872</v>
+        <v>110.757618</v>
       </c>
       <c r="N86">
-        <v>-73.2545872</v>
+        <v>-74.55761799999999</v>
       </c>
       <c r="O86">
-        <v>-18.3136468</v>
+        <v>-18.6394045</v>
       </c>
       <c r="P86">
-        <v>-54.9409404</v>
+        <v>-55.91821349999999</v>
       </c>
       <c r="Q86">
-        <v>-47.74094040000001</v>
+        <v>-48.7182135</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4404634390308835</v>
+        <v>0.4667743349662757</v>
       </c>
       <c r="T86">
-        <v>3.816697089747109</v>
+        <v>4.071143562396916</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08268269271769726</v>
+        <v>0.0817099551563126</v>
       </c>
       <c r="W86">
-        <v>0.216303421057167</v>
+        <v>0.2165327925741415</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3307307708707891</v>
+        <v>0.3268398206252504</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2540690239329616</v>
+        <v>0.2559690239329617</v>
       </c>
       <c r="C87">
-        <v>-279.0083257008673</v>
+        <v>-286.1326734253898</v>
       </c>
       <c r="D87">
-        <v>176.8016742991327</v>
+        <v>175.2033265746102</v>
       </c>
       <c r="E87">
-        <v>450.21</v>
+        <v>455.736</v>
       </c>
       <c r="F87">
-        <v>469.71</v>
+        <v>475.236</v>
       </c>
       <c r="G87">
         <v>13.9</v>
@@ -8421,37 +8421,37 @@
         <v>36.2</v>
       </c>
       <c r="M87">
-        <v>110.757618</v>
+        <v>112.0606488</v>
       </c>
       <c r="N87">
-        <v>-74.55761799999999</v>
+        <v>-75.86064879999999</v>
       </c>
       <c r="O87">
-        <v>-18.6394045</v>
+        <v>-18.9651622</v>
       </c>
       <c r="P87">
-        <v>-55.91821349999999</v>
+        <v>-56.8954866</v>
       </c>
       <c r="Q87">
-        <v>-48.7182135</v>
+        <v>-49.6954866</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4667743349662757</v>
+        <v>0.4968439303210098</v>
       </c>
       <c r="T87">
-        <v>4.071143562396916</v>
+        <v>4.361939531139553</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0817099551563126</v>
+        <v>0.08075983939868106</v>
       </c>
       <c r="W87">
-        <v>0.2165327925741415</v>
+        <v>0.216756829869791</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3268398206252504</v>
+        <v>0.3230393575947242</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2559690239329617</v>
+        <v>0.2578690239329616</v>
       </c>
       <c r="C88">
-        <v>-286.1326734253898</v>
+        <v>-293.2283808457294</v>
       </c>
       <c r="D88">
-        <v>175.2033265746102</v>
+        <v>173.6336191542706</v>
       </c>
       <c r="E88">
-        <v>455.736</v>
+        <v>461.262</v>
       </c>
       <c r="F88">
-        <v>475.236</v>
+        <v>480.762</v>
       </c>
       <c r="G88">
         <v>13.9</v>
@@ -8503,37 +8503,37 @@
         <v>36.2</v>
       </c>
       <c r="M88">
-        <v>112.0606488</v>
+        <v>113.3636796</v>
       </c>
       <c r="N88">
-        <v>-75.86064879999999</v>
+        <v>-77.16367960000001</v>
       </c>
       <c r="O88">
-        <v>-18.9651622</v>
+        <v>-19.2909199</v>
       </c>
       <c r="P88">
-        <v>-56.8954866</v>
+        <v>-57.8727597</v>
       </c>
       <c r="Q88">
-        <v>-49.6954866</v>
+        <v>-50.67275970000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4968439303210098</v>
+        <v>0.5315396172687796</v>
       </c>
       <c r="T88">
-        <v>4.361939531139553</v>
+        <v>4.69747334122721</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08075983939868106</v>
+        <v>0.07983156538260425</v>
       </c>
       <c r="W88">
-        <v>0.216756829869791</v>
+        <v>0.2169757168827819</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3230393575947242</v>
+        <v>0.319326261530417</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2578690239329616</v>
+        <v>0.2597690239329616</v>
       </c>
       <c r="C89">
-        <v>-293.2283808457294</v>
+        <v>-300.2962109215467</v>
       </c>
       <c r="D89">
-        <v>173.6336191542706</v>
+        <v>172.0917890784532</v>
       </c>
       <c r="E89">
-        <v>461.262</v>
+        <v>466.788</v>
       </c>
       <c r="F89">
-        <v>480.762</v>
+        <v>486.288</v>
       </c>
       <c r="G89">
         <v>13.9</v>
@@ -8585,37 +8585,37 @@
         <v>36.2</v>
       </c>
       <c r="M89">
-        <v>113.3636796</v>
+        <v>114.6667104</v>
       </c>
       <c r="N89">
-        <v>-77.16367960000001</v>
+        <v>-78.46671040000001</v>
       </c>
       <c r="O89">
-        <v>-19.2909199</v>
+        <v>-19.6166776</v>
       </c>
       <c r="P89">
-        <v>-57.8727597</v>
+        <v>-58.85003280000001</v>
       </c>
       <c r="Q89">
-        <v>-50.67275970000001</v>
+        <v>-51.65003280000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5315396172687796</v>
+        <v>0.5720179187078447</v>
       </c>
       <c r="T89">
-        <v>4.69747334122721</v>
+        <v>5.088929452996146</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07983156538260425</v>
+        <v>0.07892438850325648</v>
       </c>
       <c r="W89">
-        <v>0.2169757168827819</v>
+        <v>0.2171896291909321</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.319326261530417</v>
+        <v>0.3156975540130259</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2597690239329616</v>
+        <v>0.2616690239329617</v>
       </c>
       <c r="C90">
-        <v>-300.2962109215467</v>
+        <v>-307.3368997513373</v>
       </c>
       <c r="D90">
-        <v>172.0917890784532</v>
+        <v>170.5771002486626</v>
       </c>
       <c r="E90">
-        <v>466.788</v>
+        <v>472.314</v>
       </c>
       <c r="F90">
-        <v>486.288</v>
+        <v>491.814</v>
       </c>
       <c r="G90">
         <v>13.9</v>
@@ -8667,37 +8667,37 @@
         <v>36.2</v>
       </c>
       <c r="M90">
-        <v>114.6667104</v>
+        <v>115.9697412</v>
       </c>
       <c r="N90">
-        <v>-78.46671040000001</v>
+        <v>-79.76974120000001</v>
       </c>
       <c r="O90">
-        <v>-19.6166776</v>
+        <v>-19.9424353</v>
       </c>
       <c r="P90">
-        <v>-58.85003280000001</v>
+        <v>-59.82730590000001</v>
       </c>
       <c r="Q90">
-        <v>-51.65003280000001</v>
+        <v>-52.62730590000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5720179187078447</v>
+        <v>0.6198559113176487</v>
       </c>
       <c r="T90">
-        <v>5.088929452996146</v>
+        <v>5.551559403268522</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07892438850325648</v>
+        <v>0.07803759762119741</v>
       </c>
       <c r="W90">
-        <v>0.2171896291909321</v>
+        <v>0.2173987344809216</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3156975540130259</v>
+        <v>0.3121503904847897</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2616690239329617</v>
+        <v>0.2635690239329617</v>
       </c>
       <c r="C91">
-        <v>-307.3368997513373</v>
+        <v>-314.3511577442291</v>
       </c>
       <c r="D91">
-        <v>170.5771002486626</v>
+        <v>169.0888422557709</v>
       </c>
       <c r="E91">
-        <v>472.314</v>
+        <v>477.84</v>
       </c>
       <c r="F91">
-        <v>491.814</v>
+        <v>497.34</v>
       </c>
       <c r="G91">
         <v>13.9</v>
@@ -8749,37 +8749,37 @@
         <v>36.2</v>
       </c>
       <c r="M91">
-        <v>115.9697412</v>
+        <v>117.272772</v>
       </c>
       <c r="N91">
-        <v>-79.76974120000001</v>
+        <v>-81.07277200000001</v>
       </c>
       <c r="O91">
-        <v>-19.9424353</v>
+        <v>-20.268193</v>
       </c>
       <c r="P91">
-        <v>-59.82730590000001</v>
+        <v>-60.80457900000001</v>
       </c>
       <c r="Q91">
-        <v>-52.62730590000002</v>
+        <v>-53.60457900000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6198559113176487</v>
+        <v>0.6772615024494137</v>
       </c>
       <c r="T91">
-        <v>5.551559403268522</v>
+        <v>6.106715343595376</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07803759762119741</v>
+        <v>0.0771705132031841</v>
       </c>
       <c r="W91">
-        <v>0.2173987344809216</v>
+        <v>0.2176031929866892</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3121503904847897</v>
+        <v>0.3086820528127364</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2635690239329617</v>
+        <v>0.2654690239329617</v>
       </c>
       <c r="C92">
-        <v>-314.3511577442291</v>
+        <v>-321.3396707309669</v>
       </c>
       <c r="D92">
-        <v>169.0888422557709</v>
+        <v>167.6263292690331</v>
       </c>
       <c r="E92">
-        <v>477.84</v>
+        <v>483.366</v>
       </c>
       <c r="F92">
-        <v>497.34</v>
+        <v>502.866</v>
       </c>
       <c r="G92">
         <v>13.9</v>
@@ -8831,37 +8831,37 @@
         <v>36.2</v>
       </c>
       <c r="M92">
-        <v>117.272772</v>
+        <v>118.5758028</v>
       </c>
       <c r="N92">
-        <v>-81.07277200000001</v>
+        <v>-82.37580280000002</v>
       </c>
       <c r="O92">
-        <v>-20.268193</v>
+        <v>-20.5939507</v>
       </c>
       <c r="P92">
-        <v>-60.80457900000001</v>
+        <v>-61.78185210000001</v>
       </c>
       <c r="Q92">
-        <v>-53.60457900000002</v>
+        <v>-54.58185210000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6772615024494137</v>
+        <v>0.7474238916104597</v>
       </c>
       <c r="T92">
-        <v>6.106715343595376</v>
+        <v>6.785239270661529</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0771705132031841</v>
+        <v>0.0763224855855667</v>
       </c>
       <c r="W92">
-        <v>0.2176031929866892</v>
+        <v>0.2178031578989234</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3086820528127364</v>
+        <v>0.3052899423422668</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2654690239329617</v>
+        <v>0.2673690239329616</v>
       </c>
       <c r="C93">
-        <v>-321.3396707309669</v>
+        <v>-328.3031010177363</v>
       </c>
       <c r="D93">
-        <v>167.6263292690331</v>
+        <v>166.1888989822638</v>
       </c>
       <c r="E93">
-        <v>483.366</v>
+        <v>488.8920000000001</v>
       </c>
       <c r="F93">
-        <v>502.866</v>
+        <v>508.3920000000001</v>
       </c>
       <c r="G93">
         <v>13.9</v>
@@ -8913,37 +8913,37 @@
         <v>36.2</v>
       </c>
       <c r="M93">
-        <v>118.5758028</v>
+        <v>119.8788336</v>
       </c>
       <c r="N93">
-        <v>-82.37580280000002</v>
+        <v>-83.67883360000002</v>
       </c>
       <c r="O93">
-        <v>-20.5939507</v>
+        <v>-20.9197084</v>
       </c>
       <c r="P93">
-        <v>-61.78185210000001</v>
+        <v>-62.75912520000001</v>
       </c>
       <c r="Q93">
-        <v>-54.58185210000001</v>
+        <v>-55.55912520000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7474238916104597</v>
+        <v>0.8351268780617674</v>
       </c>
       <c r="T93">
-        <v>6.785239270661529</v>
+        <v>7.633394179494222</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0763224855855667</v>
+        <v>0.07549289335094098</v>
       </c>
       <c r="W93">
-        <v>0.2178031578989234</v>
+        <v>0.2179987757478481</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3052899423422668</v>
+        <v>0.3019715734037639</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2673690239329616</v>
+        <v>0.2692690239329616</v>
       </c>
       <c r="C94">
-        <v>-328.3031010177363</v>
+        <v>-335.2420883862273</v>
       </c>
       <c r="D94">
-        <v>166.1888989822638</v>
+        <v>164.7759116137727</v>
       </c>
       <c r="E94">
-        <v>488.8920000000001</v>
+        <v>494.418</v>
       </c>
       <c r="F94">
-        <v>508.3920000000001</v>
+        <v>513.918</v>
       </c>
       <c r="G94">
         <v>13.9</v>
@@ -8995,37 +8995,37 @@
         <v>36.2</v>
       </c>
       <c r="M94">
-        <v>119.8788336</v>
+        <v>121.1818644</v>
       </c>
       <c r="N94">
-        <v>-83.67883360000002</v>
+        <v>-84.98186440000001</v>
       </c>
       <c r="O94">
-        <v>-20.9197084</v>
+        <v>-21.2454661</v>
       </c>
       <c r="P94">
-        <v>-62.75912520000001</v>
+        <v>-63.7363983</v>
       </c>
       <c r="Q94">
-        <v>-55.55912520000002</v>
+        <v>-56.53639830000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8351268780617674</v>
+        <v>0.94788786064202</v>
       </c>
       <c r="T94">
-        <v>7.633394179494222</v>
+        <v>8.723879062279112</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07549289335094098</v>
+        <v>0.07468114180953302</v>
       </c>
       <c r="W94">
-        <v>0.2179987757478481</v>
+        <v>0.2181901867613121</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3019715734037639</v>
+        <v>0.298724567238132</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2692690239329616</v>
+        <v>0.2711690239329616</v>
       </c>
       <c r="C95">
-        <v>-335.2420883862273</v>
+        <v>-342.1572510431117</v>
       </c>
       <c r="D95">
-        <v>164.7759116137727</v>
+        <v>163.3867489568883</v>
       </c>
       <c r="E95">
-        <v>494.418</v>
+        <v>499.9440000000001</v>
       </c>
       <c r="F95">
-        <v>513.918</v>
+        <v>519.4440000000001</v>
       </c>
       <c r="G95">
         <v>13.9</v>
@@ -9077,37 +9077,37 @@
         <v>36.2</v>
       </c>
       <c r="M95">
-        <v>121.1818644</v>
+        <v>122.4848952</v>
       </c>
       <c r="N95">
-        <v>-84.98186440000001</v>
+        <v>-86.28489520000002</v>
       </c>
       <c r="O95">
-        <v>-21.2454661</v>
+        <v>-21.57122380000001</v>
       </c>
       <c r="P95">
-        <v>-63.7363983</v>
+        <v>-64.71367140000001</v>
       </c>
       <c r="Q95">
-        <v>-56.53639830000001</v>
+        <v>-57.51367140000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.94788786064202</v>
+        <v>1.09823583741569</v>
       </c>
       <c r="T95">
-        <v>8.723879062279112</v>
+        <v>10.1778589059923</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07468114180953302</v>
+        <v>0.07388666157751669</v>
       </c>
       <c r="W95">
-        <v>0.2181901867613121</v>
+        <v>0.2183775252000216</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.298724567238132</v>
+        <v>0.2955466463100668</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2711690239329616</v>
+        <v>0.2730690239329617</v>
       </c>
       <c r="C96">
-        <v>-342.1572510431117</v>
+        <v>-349.0491865218934</v>
       </c>
       <c r="D96">
-        <v>163.3867489568883</v>
+        <v>162.0208134781067</v>
       </c>
       <c r="E96">
-        <v>499.9440000000001</v>
+        <v>505.47</v>
       </c>
       <c r="F96">
-        <v>519.4440000000001</v>
+        <v>524.97</v>
       </c>
       <c r="G96">
         <v>13.9</v>
@@ -9159,37 +9159,37 @@
         <v>36.2</v>
       </c>
       <c r="M96">
-        <v>122.4848952</v>
+        <v>123.787926</v>
       </c>
       <c r="N96">
-        <v>-86.28489520000002</v>
+        <v>-87.58792600000001</v>
       </c>
       <c r="O96">
-        <v>-21.57122380000001</v>
+        <v>-21.8969815</v>
       </c>
       <c r="P96">
-        <v>-64.71367140000001</v>
+        <v>-65.6909445</v>
       </c>
       <c r="Q96">
-        <v>-57.51367140000001</v>
+        <v>-58.4909445</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.09823583741569</v>
+        <v>1.308723004898829</v>
       </c>
       <c r="T96">
-        <v>10.1778589059923</v>
+        <v>12.21343068719077</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07388666157751669</v>
+        <v>0.07310890724512178</v>
       </c>
       <c r="W96">
-        <v>0.2183775252000216</v>
+        <v>0.2185609196716003</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2955466463100668</v>
+        <v>0.2924356289804871</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2730690239329617</v>
+        <v>0.2749690239329617</v>
       </c>
       <c r="C97">
-        <v>-349.0491865218934</v>
+        <v>-355.9184725398958</v>
       </c>
       <c r="D97">
-        <v>162.0208134781067</v>
+        <v>160.6775274601043</v>
       </c>
       <c r="E97">
-        <v>505.47</v>
+        <v>510.9960000000001</v>
       </c>
       <c r="F97">
-        <v>524.97</v>
+        <v>530.4960000000001</v>
       </c>
       <c r="G97">
         <v>13.9</v>
@@ -9241,37 +9241,37 @@
         <v>36.2</v>
       </c>
       <c r="M97">
-        <v>123.787926</v>
+        <v>125.0909568</v>
       </c>
       <c r="N97">
-        <v>-87.58792600000001</v>
+        <v>-88.89095680000003</v>
       </c>
       <c r="O97">
-        <v>-21.8969815</v>
+        <v>-22.22273920000001</v>
       </c>
       <c r="P97">
-        <v>-65.6909445</v>
+        <v>-66.66821760000002</v>
       </c>
       <c r="Q97">
-        <v>-58.4909445</v>
+        <v>-59.46821760000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.308723004898829</v>
+        <v>1.624453756123537</v>
       </c>
       <c r="T97">
-        <v>12.21343068719077</v>
+        <v>15.26678835898847</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07310890724512178</v>
+        <v>0.0723473561279851</v>
       </c>
       <c r="W97">
-        <v>0.2185609196716003</v>
+        <v>0.2187404934250211</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2924356289804871</v>
+        <v>0.2893894245119404</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2749690239329616</v>
+        <v>0.2768690239329616</v>
       </c>
       <c r="C98">
-        <v>-355.9184725398956</v>
+        <v>-362.7656678129703</v>
       </c>
       <c r="D98">
-        <v>160.6775274601044</v>
+        <v>159.3563321870297</v>
       </c>
       <c r="E98">
-        <v>510.996</v>
+        <v>516.522</v>
       </c>
       <c r="F98">
-        <v>530.496</v>
+        <v>536.022</v>
       </c>
       <c r="G98">
         <v>13.9</v>
@@ -9323,37 +9323,37 @@
         <v>36.2</v>
       </c>
       <c r="M98">
-        <v>125.0909568</v>
+        <v>126.3939876</v>
       </c>
       <c r="N98">
-        <v>-88.8909568</v>
+        <v>-90.19398760000001</v>
       </c>
       <c r="O98">
-        <v>-22.2227392</v>
+        <v>-22.5484969</v>
       </c>
       <c r="P98">
-        <v>-66.66821759999999</v>
+        <v>-67.64549070000001</v>
       </c>
       <c r="Q98">
-        <v>-59.4682176</v>
+        <v>-60.44549070000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.624453756123533</v>
+        <v>2.150671674831377</v>
       </c>
       <c r="T98">
-        <v>15.26678835898842</v>
+        <v>20.35571781198457</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07234735612798511</v>
+        <v>0.07160150709573783</v>
       </c>
       <c r="W98">
-        <v>0.2187404934250211</v>
+        <v>0.218916364626825</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2893894245119404</v>
+        <v>0.2864060283829514</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2768690239329616</v>
+        <v>0.2787690239329617</v>
       </c>
       <c r="C99">
-        <v>-362.7656678129703</v>
+        <v>-369.5913128303374</v>
       </c>
       <c r="D99">
-        <v>159.3563321870297</v>
+        <v>158.0566871696626</v>
       </c>
       <c r="E99">
-        <v>516.522</v>
+        <v>522.048</v>
       </c>
       <c r="F99">
-        <v>536.022</v>
+        <v>541.548</v>
       </c>
       <c r="G99">
         <v>13.9</v>
@@ -9405,37 +9405,37 @@
         <v>36.2</v>
       </c>
       <c r="M99">
-        <v>126.3939876</v>
+        <v>127.6970184</v>
       </c>
       <c r="N99">
-        <v>-90.19398760000001</v>
+        <v>-91.4970184</v>
       </c>
       <c r="O99">
-        <v>-22.5484969</v>
+        <v>-22.8742546</v>
       </c>
       <c r="P99">
-        <v>-67.64549070000001</v>
+        <v>-68.6227638</v>
       </c>
       <c r="Q99">
-        <v>-60.44549070000001</v>
+        <v>-61.42276380000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.150671674831377</v>
+        <v>3.203107512247065</v>
       </c>
       <c r="T99">
-        <v>20.35571781198457</v>
+        <v>30.53357671797685</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07160150709573783</v>
+        <v>0.07087087947231194</v>
       </c>
       <c r="W99">
-        <v>0.218916364626825</v>
+        <v>0.2190886466204288</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2864060283829514</v>
+        <v>0.2834835178892477</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2787690239329617</v>
+        <v>0.2806690239329617</v>
       </c>
       <c r="C100">
-        <v>-369.5913128303374</v>
+        <v>-376.3959305918183</v>
       </c>
       <c r="D100">
-        <v>158.0566871696626</v>
+        <v>156.7780694081817</v>
       </c>
       <c r="E100">
-        <v>522.048</v>
+        <v>527.5740000000001</v>
       </c>
       <c r="F100">
-        <v>541.548</v>
+        <v>547.0740000000001</v>
       </c>
       <c r="G100">
         <v>13.9</v>
@@ -9487,37 +9487,37 @@
         <v>36.2</v>
       </c>
       <c r="M100">
-        <v>127.6970184</v>
+        <v>129.0000492</v>
       </c>
       <c r="N100">
-        <v>-91.4970184</v>
+        <v>-92.80004920000003</v>
       </c>
       <c r="O100">
-        <v>-22.8742546</v>
+        <v>-23.20001230000001</v>
       </c>
       <c r="P100">
-        <v>-68.6227638</v>
+        <v>-69.60003690000002</v>
       </c>
       <c r="Q100">
-        <v>-61.42276380000001</v>
+        <v>-62.40003690000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.203107512247065</v>
+        <v>6.360415024494131</v>
       </c>
       <c r="T100">
-        <v>30.53357671797685</v>
+        <v>61.06715343595369</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07087087947231194</v>
+        <v>0.07015501200289463</v>
       </c>
       <c r="W100">
-        <v>0.2190886466204288</v>
+        <v>0.2192574481697175</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2834835178892477</v>
+        <v>0.2806200480115786</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2806690239329617</v>
-      </c>
-      <c r="C101">
-        <v>-376.3959305918183</v>
-      </c>
-      <c r="D101">
-        <v>156.7780694081817</v>
-      </c>
-      <c r="E101">
-        <v>527.5740000000001</v>
-      </c>
-      <c r="F101">
-        <v>547.0740000000001</v>
-      </c>
-      <c r="G101">
-        <v>13.9</v>
-      </c>
-      <c r="H101">
-        <v>533.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>43.4</v>
-      </c>
-      <c r="K101">
-        <v>7.199999999999996</v>
-      </c>
-      <c r="L101">
-        <v>36.2</v>
-      </c>
-      <c r="M101">
-        <v>129.0000492</v>
-      </c>
-      <c r="N101">
-        <v>-92.80004920000003</v>
-      </c>
-      <c r="O101">
-        <v>-23.20001230000001</v>
-      </c>
-      <c r="P101">
-        <v>-69.60003690000002</v>
-      </c>
-      <c r="Q101">
-        <v>-62.40003690000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.360415024494131</v>
-      </c>
-      <c r="T101">
-        <v>61.06715343595369</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07015501200289463</v>
-      </c>
-      <c r="W101">
-        <v>0.2192574481697175</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2806200480115786</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
